--- a/Data Siswa/Clear Data/Data Siswa Salma 2026.xlsx
+++ b/Data Siswa/Clear Data/Data Siswa Salma 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Rupa-Rupa\DashboardTim\Data Siswa\Clear Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8240A675-D456-421C-AFA1-065D92C711B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC3A714-1692-49EF-B8D6-E50BF20E80C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2E616BFB-0DA7-48A4-BA17-C5DC9896544D}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5830" uniqueCount="2848">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7228" uniqueCount="3328">
   <si>
     <t>NAMA</t>
   </si>
@@ -8581,12 +8581,1455 @@
   </si>
   <si>
     <t>6282195073759</t>
+  </si>
+  <si>
+    <t>NONAME</t>
+  </si>
+  <si>
+    <t>SMA YPK 2 BIAK</t>
+  </si>
+  <si>
+    <t>6281343026010</t>
+  </si>
+  <si>
+    <t>6281283464685</t>
+  </si>
+  <si>
+    <t>6282198659641</t>
+  </si>
+  <si>
+    <t>6285282081053</t>
+  </si>
+  <si>
+    <t>6282199278674</t>
+  </si>
+  <si>
+    <t>6281247290845</t>
+  </si>
+  <si>
+    <t>6282294839630</t>
+  </si>
+  <si>
+    <t>6281343111874</t>
+  </si>
+  <si>
+    <t>6281247020730</t>
+  </si>
+  <si>
+    <t>6282251847680</t>
+  </si>
+  <si>
+    <t>6281343025951</t>
+  </si>
+  <si>
+    <t>6281247385726</t>
+  </si>
+  <si>
+    <t>6282239912545</t>
+  </si>
+  <si>
+    <t>6282343467881</t>
+  </si>
+  <si>
+    <t>6282146414093</t>
+  </si>
+  <si>
+    <t>6282190766767</t>
+  </si>
+  <si>
+    <t>6282198813757</t>
+  </si>
+  <si>
+    <t>6282239912429</t>
+  </si>
+  <si>
+    <t>6281381203516</t>
+  </si>
+  <si>
+    <t>6282190763581</t>
+  </si>
+  <si>
+    <t>6282239913523</t>
+  </si>
+  <si>
+    <t>6282336865454</t>
+  </si>
+  <si>
+    <t>6282190766790</t>
+  </si>
+  <si>
+    <t>6281248440728</t>
+  </si>
+  <si>
+    <t>6282199323106</t>
+  </si>
+  <si>
+    <t>6282122345137</t>
+  </si>
+  <si>
+    <t>6282199339510</t>
+  </si>
+  <si>
+    <t>6281258491618</t>
+  </si>
+  <si>
+    <t>6282198966534</t>
+  </si>
+  <si>
+    <t>6282336864441</t>
+  </si>
+  <si>
+    <t>6282148399174</t>
+  </si>
+  <si>
+    <t>628134486447</t>
+  </si>
+  <si>
+    <t>SMA YPPK 2 BIAK</t>
+  </si>
+  <si>
+    <t>62082199360824</t>
+  </si>
+  <si>
+    <t>62082199581992</t>
+  </si>
+  <si>
+    <t>62081343118836</t>
+  </si>
+  <si>
+    <t>62085244802457</t>
+  </si>
+  <si>
+    <t>62081393965605</t>
+  </si>
+  <si>
+    <t>6281393965605</t>
+  </si>
+  <si>
+    <t>6282199824518</t>
+  </si>
+  <si>
+    <t>6282113053872</t>
+  </si>
+  <si>
+    <t>6282124319055</t>
+  </si>
+  <si>
+    <t>6282198123580</t>
+  </si>
+  <si>
+    <t>6282199552541</t>
+  </si>
+  <si>
+    <t>6285235413793</t>
+  </si>
+  <si>
+    <t>6282199379378</t>
+  </si>
+  <si>
+    <t>6281343132229</t>
+  </si>
+  <si>
+    <t>6282251841921</t>
+  </si>
+  <si>
+    <t>6282239910806</t>
+  </si>
+  <si>
+    <t>6282251839656</t>
+  </si>
+  <si>
+    <t>6281240341327</t>
+  </si>
+  <si>
+    <t>6281248879247</t>
+  </si>
+  <si>
+    <t>6281343139985</t>
+  </si>
+  <si>
+    <t>6281263388150</t>
+  </si>
+  <si>
+    <t>6282199277806</t>
+  </si>
+  <si>
+    <t>6281247031833</t>
+  </si>
+  <si>
+    <t>6282199258364</t>
+  </si>
+  <si>
+    <t>6282132912995</t>
+  </si>
+  <si>
+    <t>6282272049537</t>
+  </si>
+  <si>
+    <t>6282199580113</t>
+  </si>
+  <si>
+    <t>6282199824206</t>
+  </si>
+  <si>
+    <t>6281231351331</t>
+  </si>
+  <si>
+    <t>6281343113556</t>
+  </si>
+  <si>
+    <t>6281324597484</t>
+  </si>
+  <si>
+    <t>6281249357210</t>
+  </si>
+  <si>
+    <t>6281248140519</t>
+  </si>
+  <si>
+    <t>6281248773949</t>
+  </si>
+  <si>
+    <t>628219958050</t>
+  </si>
+  <si>
+    <t>6282190913913</t>
+  </si>
+  <si>
+    <t>6281248749976</t>
+  </si>
+  <si>
+    <t>6282374629931</t>
+  </si>
+  <si>
+    <t>6282211065490</t>
+  </si>
+  <si>
+    <t>6282131430996</t>
+  </si>
+  <si>
+    <t>6282251893393</t>
+  </si>
+  <si>
+    <t>6282248404232</t>
+  </si>
+  <si>
+    <t>6281343034097</t>
+  </si>
+  <si>
+    <t>6282198659822</t>
+  </si>
+  <si>
+    <t>6281389567802</t>
+  </si>
+  <si>
+    <t>6282198967656</t>
+  </si>
+  <si>
+    <t>6281248130228</t>
+  </si>
+  <si>
+    <t>6282198145879</t>
+  </si>
+  <si>
+    <t>6282148390465</t>
+  </si>
+  <si>
+    <t>6281248594668</t>
+  </si>
+  <si>
+    <t>6281262449206</t>
+  </si>
+  <si>
+    <t>6285753261436</t>
+  </si>
+  <si>
+    <t>6282198980773</t>
+  </si>
+  <si>
+    <t>6281240182667</t>
+  </si>
+  <si>
+    <t>6281238639606</t>
+  </si>
+  <si>
+    <t>6282198456134</t>
+  </si>
+  <si>
+    <t>6281240887125</t>
+  </si>
+  <si>
+    <t>6282251849645</t>
+  </si>
+  <si>
+    <t>6281248194711</t>
+  </si>
+  <si>
+    <t>6281343110686</t>
+  </si>
+  <si>
+    <t>6281348032269</t>
+  </si>
+  <si>
+    <t>6281361840763</t>
+  </si>
+  <si>
+    <t>6281344604535</t>
+  </si>
+  <si>
+    <t>6282252869303</t>
+  </si>
+  <si>
+    <t>6281247029430</t>
+  </si>
+  <si>
+    <t>6281248064025</t>
+  </si>
+  <si>
+    <t>6281367287706</t>
+  </si>
+  <si>
+    <t>6281247524521</t>
+  </si>
+  <si>
+    <t>SMA NEGERI 1 KOTA BIAK</t>
+  </si>
+  <si>
+    <t>6282239153910</t>
+  </si>
+  <si>
+    <t>6282248412892</t>
+  </si>
+  <si>
+    <t>6281216449225</t>
+  </si>
+  <si>
+    <t>6282110089155</t>
+  </si>
+  <si>
+    <t>6282190824131</t>
+  </si>
+  <si>
+    <t>6281383201471</t>
+  </si>
+  <si>
+    <t>6281344320080</t>
+  </si>
+  <si>
+    <t>6282182158487</t>
+  </si>
+  <si>
+    <t>628134890995</t>
+  </si>
+  <si>
+    <t>6285243251261</t>
+  </si>
+  <si>
+    <t>6281248091085</t>
+  </si>
+  <si>
+    <t>6285299528325</t>
+  </si>
+  <si>
+    <t>6282198276544</t>
+  </si>
+  <si>
+    <t>6281244651375</t>
+  </si>
+  <si>
+    <t>6282113290335</t>
+  </si>
+  <si>
+    <t>62813213121790</t>
+  </si>
+  <si>
+    <t>6281247063654</t>
+  </si>
+  <si>
+    <t>6281248267168</t>
+  </si>
+  <si>
+    <t>6282198385412</t>
+  </si>
+  <si>
+    <t>6282148389904</t>
+  </si>
+  <si>
+    <t>6281248289252</t>
+  </si>
+  <si>
+    <t>6281248581691</t>
+  </si>
+  <si>
+    <t>6282238222597</t>
+  </si>
+  <si>
+    <t>6281248848449</t>
+  </si>
+  <si>
+    <t>6282199252532</t>
+  </si>
+  <si>
+    <t>6282239037036</t>
+  </si>
+  <si>
+    <t>6281344004574</t>
+  </si>
+  <si>
+    <t>6281247764252</t>
+  </si>
+  <si>
+    <t>6281344899760</t>
+  </si>
+  <si>
+    <t>6281247902251</t>
+  </si>
+  <si>
+    <t>6282248327987</t>
+  </si>
+  <si>
+    <t>6282498675988</t>
+  </si>
+  <si>
+    <t>6282789885268</t>
+  </si>
+  <si>
+    <t>6282199824550</t>
+  </si>
+  <si>
+    <t>6282190922083</t>
+  </si>
+  <si>
+    <t>6281139912008</t>
+  </si>
+  <si>
+    <t>6281343033457</t>
+  </si>
+  <si>
+    <t>6281343074167</t>
+  </si>
+  <si>
+    <t>6282198386293</t>
+  </si>
+  <si>
+    <t>6282199277186</t>
+  </si>
+  <si>
+    <t>6282395655661</t>
+  </si>
+  <si>
+    <t>6281248140154</t>
+  </si>
+  <si>
+    <t>6281343118369</t>
+  </si>
+  <si>
+    <t>6282198745073</t>
+  </si>
+  <si>
+    <t>6282399958397</t>
+  </si>
+  <si>
+    <t>6285392165197</t>
+  </si>
+  <si>
+    <t>6281247251160</t>
+  </si>
+  <si>
+    <t>6281247631142</t>
+  </si>
+  <si>
+    <t>SMK YPK 2 BIAK</t>
+  </si>
+  <si>
+    <t>6282190903382</t>
+  </si>
+  <si>
+    <t>6281344130143</t>
+  </si>
+  <si>
+    <t>6281248441811</t>
+  </si>
+  <si>
+    <t>6282197790601</t>
+  </si>
+  <si>
+    <t>6281343263105</t>
+  </si>
+  <si>
+    <t>6282148182149</t>
+  </si>
+  <si>
+    <t>6282399833575</t>
+  </si>
+  <si>
+    <t>6282199837997</t>
+  </si>
+  <si>
+    <t>6282148385491</t>
+  </si>
+  <si>
+    <t>6282199251173</t>
+  </si>
+  <si>
+    <t>6281247028980</t>
+  </si>
+  <si>
+    <t>6282199554170</t>
+  </si>
+  <si>
+    <t>6282199304821</t>
+  </si>
+  <si>
+    <t>6282211065439</t>
+  </si>
+  <si>
+    <t>6281251771151</t>
+  </si>
+  <si>
+    <t>6282190903518</t>
+  </si>
+  <si>
+    <t>6285251639634</t>
+  </si>
+  <si>
+    <t>6282199579921</t>
+  </si>
+  <si>
+    <t>6281248393597</t>
+  </si>
+  <si>
+    <t>6282199277011</t>
+  </si>
+  <si>
+    <t>6281299339748</t>
+  </si>
+  <si>
+    <t>6285243250729</t>
+  </si>
+  <si>
+    <t>628134452699</t>
+  </si>
+  <si>
+    <t>6285292711103</t>
+  </si>
+  <si>
+    <t>6281240887670</t>
+  </si>
+  <si>
+    <t>628134457913</t>
+  </si>
+  <si>
+    <t>SMA YPK 1 BIAK</t>
+  </si>
+  <si>
+    <t>6281320965513</t>
+  </si>
+  <si>
+    <t>6285212818420</t>
+  </si>
+  <si>
+    <t>6282251623239</t>
+  </si>
+  <si>
+    <t>6285825380737</t>
+  </si>
+  <si>
+    <t>6281343139015</t>
+  </si>
+  <si>
+    <t>6281292009799</t>
+  </si>
+  <si>
+    <t>6281225460505</t>
+  </si>
+  <si>
+    <t>6282261493762</t>
+  </si>
+  <si>
+    <t>6281353657231</t>
+  </si>
+  <si>
+    <t>6282195302260</t>
+  </si>
+  <si>
+    <t>6281248622339</t>
+  </si>
+  <si>
+    <t>6281343448433</t>
+  </si>
+  <si>
+    <t>6282197656933</t>
+  </si>
+  <si>
+    <t>628134303347</t>
+  </si>
+  <si>
+    <t>6285244534922</t>
+  </si>
+  <si>
+    <t>628134891129</t>
+  </si>
+  <si>
+    <t>6289518008150</t>
+  </si>
+  <si>
+    <t>6282364168539</t>
+  </si>
+  <si>
+    <t>6281312866112</t>
+  </si>
+  <si>
+    <t>6285825158324</t>
+  </si>
+  <si>
+    <t>6281343139245</t>
+  </si>
+  <si>
+    <t>628134502997</t>
+  </si>
+  <si>
+    <t>6281343122169</t>
+  </si>
+  <si>
+    <t>6281343031840</t>
+  </si>
+  <si>
+    <t>6282199275144</t>
+  </si>
+  <si>
+    <t>SMA 3 BIAK</t>
+  </si>
+  <si>
+    <t>6282199251293</t>
+  </si>
+  <si>
+    <t>6282251615399</t>
+  </si>
+  <si>
+    <t>6282239913288</t>
+  </si>
+  <si>
+    <t>6281361712165</t>
+  </si>
+  <si>
+    <t>6282348983446</t>
+  </si>
+  <si>
+    <t>6281248086969</t>
+  </si>
+  <si>
+    <t>6285251389148</t>
+  </si>
+  <si>
+    <t>6282143834521</t>
+  </si>
+  <si>
+    <t>6282148530699</t>
+  </si>
+  <si>
+    <t>6282198835433</t>
+  </si>
+  <si>
+    <t>628134486263</t>
+  </si>
+  <si>
+    <t>6281248747370</t>
+  </si>
+  <si>
+    <t>6281248710065</t>
+  </si>
+  <si>
+    <t>6282197580224</t>
+  </si>
+  <si>
+    <t>6281247027502</t>
+  </si>
+  <si>
+    <t>6281240811871</t>
+  </si>
+  <si>
+    <t>6282190770522</t>
+  </si>
+  <si>
+    <t>6281248194874</t>
+  </si>
+  <si>
+    <t>6285285557651</t>
+  </si>
+  <si>
+    <t>62852542715</t>
+  </si>
+  <si>
+    <t>6282399161867</t>
+  </si>
+  <si>
+    <t>6282190920559</t>
+  </si>
+  <si>
+    <t>6285211413614</t>
+  </si>
+  <si>
+    <t>6281343034136</t>
+  </si>
+  <si>
+    <t>62813430735593</t>
+  </si>
+  <si>
+    <t>6282399612687</t>
+  </si>
+  <si>
+    <t>6281343292909</t>
+  </si>
+  <si>
+    <t>6282211238978</t>
+  </si>
+  <si>
+    <t>6282198563113</t>
+  </si>
+  <si>
+    <t>BEATRIX B. MIMITAUW</t>
+  </si>
+  <si>
+    <t>SMKN 8 JAYAPURA</t>
+  </si>
+  <si>
+    <t>0813448134</t>
+  </si>
+  <si>
+    <t>JAMES ANDIKA RERUNG</t>
+  </si>
+  <si>
+    <t>081245132631</t>
+  </si>
+  <si>
+    <t>HAIKAL ARYA DUTA</t>
+  </si>
+  <si>
+    <t>081247017508</t>
+  </si>
+  <si>
+    <t>PAI TABUNI</t>
+  </si>
+  <si>
+    <t>082146324570</t>
+  </si>
+  <si>
+    <t>SOSTENES KAYAME</t>
+  </si>
+  <si>
+    <t>085251173902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DEMAS URWAN </t>
+  </si>
+  <si>
+    <t>082197991867</t>
+  </si>
+  <si>
+    <t>MIKAIL A. SOAMOLE</t>
+  </si>
+  <si>
+    <t>081340978168</t>
+  </si>
+  <si>
+    <t>VALEN SIPAYUNG</t>
+  </si>
+  <si>
+    <t>085761291583</t>
+  </si>
+  <si>
+    <t>ARISON NEWEGALEN</t>
+  </si>
+  <si>
+    <t>085339096979</t>
+  </si>
+  <si>
+    <t>AHMAD RIVKI ALVIN</t>
+  </si>
+  <si>
+    <t>082298111935</t>
+  </si>
+  <si>
+    <t>WIYAMS D. ANSAKA</t>
+  </si>
+  <si>
+    <t>082199269407</t>
+  </si>
+  <si>
+    <t>KORNELIVS</t>
+  </si>
+  <si>
+    <t>SMA YPK TERUNA DHARMA</t>
+  </si>
+  <si>
+    <t>62812262623190</t>
+  </si>
+  <si>
+    <t>LAURA</t>
+  </si>
+  <si>
+    <t>6282343613729</t>
+  </si>
+  <si>
+    <t>MEYCINDA</t>
+  </si>
+  <si>
+    <t>6281248435488</t>
+  </si>
+  <si>
+    <t>YANI ENEMBE</t>
+  </si>
+  <si>
+    <t>6281218565717</t>
+  </si>
+  <si>
+    <t>AUDREY TENDEAN</t>
+  </si>
+  <si>
+    <t>6285210788887</t>
+  </si>
+  <si>
+    <t>JACKY</t>
+  </si>
+  <si>
+    <t>6282199104407</t>
+  </si>
+  <si>
+    <t>CHANZA</t>
+  </si>
+  <si>
+    <t>6283143170669</t>
+  </si>
+  <si>
+    <t>CHELSY</t>
+  </si>
+  <si>
+    <t>6281240869956</t>
+  </si>
+  <si>
+    <t>ANASTASIA</t>
+  </si>
+  <si>
+    <t>6282272050308</t>
+  </si>
+  <si>
+    <t>REVALDHY</t>
+  </si>
+  <si>
+    <t>6282190027165</t>
+  </si>
+  <si>
+    <t>R0SSARINA</t>
+  </si>
+  <si>
+    <t>6282186348396</t>
+  </si>
+  <si>
+    <t>DINDA B.D</t>
+  </si>
+  <si>
+    <t>6282198079395</t>
+  </si>
+  <si>
+    <t>MEIDY</t>
+  </si>
+  <si>
+    <t>6285311739457</t>
+  </si>
+  <si>
+    <t>MAXWELL</t>
+  </si>
+  <si>
+    <t>6282396088651</t>
+  </si>
+  <si>
+    <t>ALDRINA</t>
+  </si>
+  <si>
+    <t>6282189680106</t>
+  </si>
+  <si>
+    <t>FRISKHILA</t>
+  </si>
+  <si>
+    <t>6281318825030</t>
+  </si>
+  <si>
+    <t>SEBASTIAN</t>
+  </si>
+  <si>
+    <t>6282377482211</t>
+  </si>
+  <si>
+    <t>DSKAR DOGOPIA</t>
+  </si>
+  <si>
+    <t>62</t>
+  </si>
+  <si>
+    <t>STELLA FRIDA</t>
+  </si>
+  <si>
+    <t>6282199321887</t>
+  </si>
+  <si>
+    <t>BENAIAH MARPAUNG</t>
+  </si>
+  <si>
+    <t>6281247955432</t>
+  </si>
+  <si>
+    <t>VARREL SERAFLY</t>
+  </si>
+  <si>
+    <t>62827769503668</t>
+  </si>
+  <si>
+    <t>AIMEEN</t>
+  </si>
+  <si>
+    <t>6282199108794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VICTORIA </t>
+  </si>
+  <si>
+    <t>6281280109381</t>
+  </si>
+  <si>
+    <t>BRIATA</t>
+  </si>
+  <si>
+    <t>62895320697915</t>
+  </si>
+  <si>
+    <t>YULIANI</t>
+  </si>
+  <si>
+    <t>6281240203313</t>
+  </si>
+  <si>
+    <t>STEWART P.P</t>
+  </si>
+  <si>
+    <t>6282199451074</t>
+  </si>
+  <si>
+    <t>STENLY</t>
+  </si>
+  <si>
+    <t>6281377138655</t>
+  </si>
+  <si>
+    <t>REVALHO SULO</t>
+  </si>
+  <si>
+    <t>6282190027206</t>
+  </si>
+  <si>
+    <t>PRILLY A.E</t>
+  </si>
+  <si>
+    <t>6282125265708</t>
+  </si>
+  <si>
+    <t>GERAIDUS</t>
+  </si>
+  <si>
+    <t>6282198084808</t>
+  </si>
+  <si>
+    <t>MARSELA</t>
+  </si>
+  <si>
+    <t>6281223815050</t>
+  </si>
+  <si>
+    <t>ISABELLA</t>
+  </si>
+  <si>
+    <t>6281268527652</t>
+  </si>
+  <si>
+    <t>FEBRIANI</t>
+  </si>
+  <si>
+    <t>6281389515469</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>6281148807282</t>
+  </si>
+  <si>
+    <t>LIONEL</t>
+  </si>
+  <si>
+    <t>6282197805023</t>
+  </si>
+  <si>
+    <t>ANGELA</t>
+  </si>
+  <si>
+    <t>6282199576401</t>
+  </si>
+  <si>
+    <t>CHRISTIYANI</t>
+  </si>
+  <si>
+    <t>6281264884169</t>
+  </si>
+  <si>
+    <t>LOVELINA</t>
+  </si>
+  <si>
+    <t>6282157858621</t>
+  </si>
+  <si>
+    <t>NATALIA</t>
+  </si>
+  <si>
+    <t>622198455411</t>
+  </si>
+  <si>
+    <t>CHELSI</t>
+  </si>
+  <si>
+    <t>6282131006733</t>
+  </si>
+  <si>
+    <t>ELSA SUWAE</t>
+  </si>
+  <si>
+    <t>6281240369567</t>
+  </si>
+  <si>
+    <t>JESSICA</t>
+  </si>
+  <si>
+    <t>6281240162717</t>
+  </si>
+  <si>
+    <t>MARLIA C. B. PAGAPPONG</t>
+  </si>
+  <si>
+    <t>081244297515</t>
+  </si>
+  <si>
+    <t>TASYA AMANDA</t>
+  </si>
+  <si>
+    <t>081228714821</t>
+  </si>
+  <si>
+    <t>NANDA MAULYDHINA</t>
+  </si>
+  <si>
+    <t>081255396425</t>
+  </si>
+  <si>
+    <t>JUANITO S. IMBIRI</t>
+  </si>
+  <si>
+    <t>082199565762</t>
+  </si>
+  <si>
+    <t>MERSIA TAMPANG</t>
+  </si>
+  <si>
+    <t>085210851136</t>
+  </si>
+  <si>
+    <t>MARCELINO G. P. RAHAWARIN</t>
+  </si>
+  <si>
+    <t>082198631780</t>
+  </si>
+  <si>
+    <t>RADO WANGGAI</t>
+  </si>
+  <si>
+    <t>082312109782</t>
+  </si>
+  <si>
+    <t>MAYSTI G. RANTA</t>
+  </si>
+  <si>
+    <t>081343388122</t>
+  </si>
+  <si>
+    <t>SATRIA SILFANUS SILITONGA</t>
+  </si>
+  <si>
+    <t>082345379408</t>
+  </si>
+  <si>
+    <t>RACHEL MOFU</t>
+  </si>
+  <si>
+    <t>085251764185</t>
+  </si>
+  <si>
+    <t>IVY AZKARA</t>
+  </si>
+  <si>
+    <t>THEIS SAMALLO</t>
+  </si>
+  <si>
+    <t>082116700162</t>
+  </si>
+  <si>
+    <t>TRISTAN BAGUS ARMANDA</t>
+  </si>
+  <si>
+    <t>081312980063</t>
+  </si>
+  <si>
+    <t>NATATJA SARUANI</t>
+  </si>
+  <si>
+    <t>SMKN 3 JAYAPURA</t>
+  </si>
+  <si>
+    <t>082254500847</t>
+  </si>
+  <si>
+    <t>INO YOBI</t>
+  </si>
+  <si>
+    <t>085233740614</t>
+  </si>
+  <si>
+    <t>FEBROMAN DONEL BIR</t>
+  </si>
+  <si>
+    <t>081229764820</t>
+  </si>
+  <si>
+    <t>DWI RISNAYA</t>
+  </si>
+  <si>
+    <t>081223808866</t>
+  </si>
+  <si>
+    <t>MUHAMMAD FAIRUS N.</t>
+  </si>
+  <si>
+    <t>082398067006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AGUSTINUS LIONEL AUSTIN </t>
+  </si>
+  <si>
+    <t>081356962338</t>
+  </si>
+  <si>
+    <t>AERIA</t>
+  </si>
+  <si>
+    <t>085272465917</t>
+  </si>
+  <si>
+    <t>MUHAMMAD FANDY</t>
+  </si>
+  <si>
+    <t>085376866039</t>
+  </si>
+  <si>
+    <t>JHON S. MARINI</t>
+  </si>
+  <si>
+    <t>081341930701</t>
+  </si>
+  <si>
+    <t>LIDYA MARISKA L. Y. MIDAS</t>
+  </si>
+  <si>
+    <t>081247380389</t>
+  </si>
+  <si>
+    <t>SABRI ADI</t>
+  </si>
+  <si>
+    <t>SMKN 7 JAYAPURA</t>
+  </si>
+  <si>
+    <t>082267531083</t>
+  </si>
+  <si>
+    <t>MUHAMMAD RAYHAN</t>
+  </si>
+  <si>
+    <t>ANDIKA YUDISTIRA</t>
+  </si>
+  <si>
+    <t>081323645173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BAYU PRAMUDTJA </t>
+  </si>
+  <si>
+    <t>082299838887</t>
+  </si>
+  <si>
+    <t>ZASKIA EKA FAJARUROH</t>
+  </si>
+  <si>
+    <t>081253635386</t>
+  </si>
+  <si>
+    <t>ANISA FITRAH HESTARI</t>
+  </si>
+  <si>
+    <t>082393749443</t>
+  </si>
+  <si>
+    <t>LEVINA RUMBARAR</t>
+  </si>
+  <si>
+    <t>082138391800</t>
+  </si>
+  <si>
+    <t>ADIL SUHARDI</t>
+  </si>
+  <si>
+    <t>082210087535</t>
+  </si>
+  <si>
+    <t>NADYA SISILIA PUTRI</t>
+  </si>
+  <si>
+    <t>082199273392</t>
+  </si>
+  <si>
+    <t>BRIAN KOHUNUSSA</t>
+  </si>
+  <si>
+    <t>082199336553</t>
+  </si>
+  <si>
+    <t>FANHELEN DEAJENG AMIRANDA</t>
+  </si>
+  <si>
+    <t>082198289873</t>
+  </si>
+  <si>
+    <t>VERA DEWI PERTAMI</t>
+  </si>
+  <si>
+    <t>085257046727</t>
+  </si>
+  <si>
+    <t>OLIVIA NAILA SARI</t>
+  </si>
+  <si>
+    <t>082189031671</t>
+  </si>
+  <si>
+    <t>AHMAD KAUTSAR</t>
+  </si>
+  <si>
+    <t>SMA MUHAMMADIYAH JAYAPURA</t>
+  </si>
+  <si>
+    <t>081344832863</t>
+  </si>
+  <si>
+    <t>TIO PUTRA SADEWA</t>
+  </si>
+  <si>
+    <t>085241572422</t>
+  </si>
+  <si>
+    <t>RIRIN DWI IRYANTI</t>
+  </si>
+  <si>
+    <t>082137778997</t>
+  </si>
+  <si>
+    <t>FAHRIMA MAYULANI RUSLI</t>
+  </si>
+  <si>
+    <t>085397899441</t>
+  </si>
+  <si>
+    <t>M. RIZKY ANSHAR</t>
+  </si>
+  <si>
+    <t>081247124488</t>
+  </si>
+  <si>
+    <t>NUR FADHILAH ARIEF</t>
+  </si>
+  <si>
+    <t>085298382494</t>
+  </si>
+  <si>
+    <t>MUH. FAREZ</t>
+  </si>
+  <si>
+    <t>082292331611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NABIL ABDIL RAHMAN </t>
+  </si>
+  <si>
+    <t>082261038159</t>
+  </si>
+  <si>
+    <t>MOH. ISMAIL ADI WIJAYA</t>
+  </si>
+  <si>
+    <t>082198325432</t>
+  </si>
+  <si>
+    <t>MUHAMMAD RIFAT</t>
+  </si>
+  <si>
+    <t>085219849135</t>
+  </si>
+  <si>
+    <t>MARSELLA FEBIASIYAH</t>
+  </si>
+  <si>
+    <t>082199575844</t>
+  </si>
+  <si>
+    <t>AYU IFTA KHUL JANNAH</t>
+  </si>
+  <si>
+    <t>081264980673</t>
+  </si>
+  <si>
+    <t>ALVIAN MUBARAK</t>
+  </si>
+  <si>
+    <t>082399859505</t>
+  </si>
+  <si>
+    <t>LAODE AL MALIK</t>
+  </si>
+  <si>
+    <t>081244143937</t>
+  </si>
+  <si>
+    <t>ZALFA NAQIYYAH ANHAR</t>
+  </si>
+  <si>
+    <t>082197596244</t>
+  </si>
+  <si>
+    <t>JUWITA NUR ASYIFA</t>
+  </si>
+  <si>
+    <t>085784721368</t>
+  </si>
+  <si>
+    <t>DEVA AL BUCHARI</t>
+  </si>
+  <si>
+    <t>0853353494423</t>
+  </si>
+  <si>
+    <t>LAODE HASBAR</t>
+  </si>
+  <si>
+    <t>085251635494</t>
+  </si>
+  <si>
+    <t>TIARA SUCI RAMADAN</t>
+  </si>
+  <si>
+    <t>082241507190</t>
+  </si>
+  <si>
+    <t>WAODE MUSTIKA INDRIANI</t>
+  </si>
+  <si>
+    <t>081244143419</t>
+  </si>
+  <si>
+    <t>SYIFAYLA MAHARANI</t>
+  </si>
+  <si>
+    <t>081344493765</t>
+  </si>
+  <si>
+    <t>PUTRI DEWI SINTA KADIR</t>
+  </si>
+  <si>
+    <t>0872398027542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REHULINA KARINANA </t>
+  </si>
+  <si>
+    <t>082239361062</t>
+  </si>
+  <si>
+    <t>NABILA AMIRA Y.</t>
+  </si>
+  <si>
+    <t>085251343930</t>
+  </si>
+  <si>
+    <t>AL MAIRA LUTFIANA ADI PUTRI</t>
+  </si>
+  <si>
+    <t>082189105007</t>
+  </si>
+  <si>
+    <t>LAILA MUFARIKHO</t>
+  </si>
+  <si>
+    <t>081225742070</t>
+  </si>
+  <si>
+    <t>RIFKY ALVIANSYAH</t>
+  </si>
+  <si>
+    <t>082379872973</t>
+  </si>
+  <si>
+    <t>MOHAMMAT HADORI</t>
+  </si>
+  <si>
+    <t>085785050432</t>
+  </si>
+  <si>
+    <t>PUTRI NU LIA</t>
+  </si>
+  <si>
+    <t>081247075722</t>
+  </si>
+  <si>
+    <t>DIAH ANANDA DWI SAFITRI</t>
+  </si>
+  <si>
+    <t>081329204914</t>
+  </si>
+  <si>
+    <t>LINA FADILA</t>
+  </si>
+  <si>
+    <t>085251677740</t>
+  </si>
+  <si>
+    <t>SYALWA RAHMANIYAH WATTIMENA</t>
+  </si>
+  <si>
+    <t>085254082753</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0000\ 0000\ 0000"/>
+  </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -8637,7 +10080,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8661,6 +10104,16 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8976,12 +10429,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28C6D041-C50F-4542-B3B0-C667B559EA6D}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:I1459"/>
+  <dimension ref="A1:I1809"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
     <col min="2" max="2" width="35.453125" customWidth="1"/>
-    <col min="3" max="3" width="23.54296875" customWidth="1"/>
+    <col min="3" max="3" width="29.90625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.08984375" style="5" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="19.90625" style="5" bestFit="1" customWidth="1"/>
@@ -34378,7 +35831,7 @@
     </row>
     <row r="1412" spans="1:5" hidden="1" x14ac:dyDescent="0.35">
       <c r="A1412">
-        <f t="shared" ref="A1412:A1459" si="22">A1411+1</f>
+        <f t="shared" ref="A1412:A1475" si="22">A1411+1</f>
         <v>1411</v>
       </c>
       <c r="B1412" t="s">
@@ -35237,6 +36690,6302 @@
         <v>2847</v>
       </c>
       <c r="E1459" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1460" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1460">
+        <f t="shared" si="22"/>
+        <v>1459</v>
+      </c>
+      <c r="B1460" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1460" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1460" s="9" t="s">
+        <v>2850</v>
+      </c>
+      <c r="E1460" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1461" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1461">
+        <f t="shared" si="22"/>
+        <v>1460</v>
+      </c>
+      <c r="B1461" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1461" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1461" s="9" t="s">
+        <v>2851</v>
+      </c>
+      <c r="E1461" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1462" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1462">
+        <f t="shared" si="22"/>
+        <v>1461</v>
+      </c>
+      <c r="B1462" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1462" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1462" s="9" t="s">
+        <v>2852</v>
+      </c>
+      <c r="E1462" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1463">
+        <f t="shared" si="22"/>
+        <v>1462</v>
+      </c>
+      <c r="B1463" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1463" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1463" s="9" t="s">
+        <v>2853</v>
+      </c>
+      <c r="E1463" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1464">
+        <f t="shared" si="22"/>
+        <v>1463</v>
+      </c>
+      <c r="B1464" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1464" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1464" s="9" t="s">
+        <v>2854</v>
+      </c>
+      <c r="E1464" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1465" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1465">
+        <f t="shared" si="22"/>
+        <v>1464</v>
+      </c>
+      <c r="B1465" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1465" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1465" s="9" t="s">
+        <v>2855</v>
+      </c>
+      <c r="E1465" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1466" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1466">
+        <f t="shared" si="22"/>
+        <v>1465</v>
+      </c>
+      <c r="B1466" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1466" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1466" s="9" t="s">
+        <v>2856</v>
+      </c>
+      <c r="E1466" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1467" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1467">
+        <f t="shared" si="22"/>
+        <v>1466</v>
+      </c>
+      <c r="B1467" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1467" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1467" s="9" t="s">
+        <v>2857</v>
+      </c>
+      <c r="E1467" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1468" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1468">
+        <f t="shared" si="22"/>
+        <v>1467</v>
+      </c>
+      <c r="B1468" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1468" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1468" s="9" t="s">
+        <v>2858</v>
+      </c>
+      <c r="E1468" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1469" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1469">
+        <f t="shared" si="22"/>
+        <v>1468</v>
+      </c>
+      <c r="B1469" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1469" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1469" s="9" t="s">
+        <v>2859</v>
+      </c>
+      <c r="E1469" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1470" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1470">
+        <f t="shared" si="22"/>
+        <v>1469</v>
+      </c>
+      <c r="B1470" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1470" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1470" s="9" t="s">
+        <v>2860</v>
+      </c>
+      <c r="E1470" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1471" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1471">
+        <f t="shared" si="22"/>
+        <v>1470</v>
+      </c>
+      <c r="B1471" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1471" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1471" s="9" t="s">
+        <v>2861</v>
+      </c>
+      <c r="E1471" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1472" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1472">
+        <f t="shared" si="22"/>
+        <v>1471</v>
+      </c>
+      <c r="B1472" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1472" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1472" s="9" t="s">
+        <v>2862</v>
+      </c>
+      <c r="E1472" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1473" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1473">
+        <f t="shared" si="22"/>
+        <v>1472</v>
+      </c>
+      <c r="B1473" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1473" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1473" s="9" t="s">
+        <v>2863</v>
+      </c>
+      <c r="E1473" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1474" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1474">
+        <f t="shared" si="22"/>
+        <v>1473</v>
+      </c>
+      <c r="B1474" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1474" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1474" s="9" t="s">
+        <v>2864</v>
+      </c>
+      <c r="E1474" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1475" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1475">
+        <f t="shared" si="22"/>
+        <v>1474</v>
+      </c>
+      <c r="B1475" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1475" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1475" s="9" t="s">
+        <v>2865</v>
+      </c>
+      <c r="E1475" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1476" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1476">
+        <f t="shared" ref="A1476:A1539" si="23">A1475+1</f>
+        <v>1475</v>
+      </c>
+      <c r="B1476" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1476" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1476" s="9" t="s">
+        <v>2866</v>
+      </c>
+      <c r="E1476" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1477" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1477">
+        <f t="shared" si="23"/>
+        <v>1476</v>
+      </c>
+      <c r="B1477" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1477" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1477" s="9" t="s">
+        <v>2867</v>
+      </c>
+      <c r="E1477" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1478" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1478">
+        <f t="shared" si="23"/>
+        <v>1477</v>
+      </c>
+      <c r="B1478" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1478" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1478" s="9" t="s">
+        <v>2868</v>
+      </c>
+      <c r="E1478" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1479" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1479">
+        <f t="shared" si="23"/>
+        <v>1478</v>
+      </c>
+      <c r="B1479" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1479" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1479" s="9" t="s">
+        <v>2869</v>
+      </c>
+      <c r="E1479" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1480" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1480">
+        <f t="shared" si="23"/>
+        <v>1479</v>
+      </c>
+      <c r="B1480" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1480" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1480" s="9" t="s">
+        <v>2870</v>
+      </c>
+      <c r="E1480" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1481" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1481">
+        <f t="shared" si="23"/>
+        <v>1480</v>
+      </c>
+      <c r="B1481" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1481" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1481" s="9" t="s">
+        <v>2871</v>
+      </c>
+      <c r="E1481" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1482" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1482">
+        <f t="shared" si="23"/>
+        <v>1481</v>
+      </c>
+      <c r="B1482" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1482" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1482" s="9" t="s">
+        <v>2872</v>
+      </c>
+      <c r="E1482" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1483" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1483">
+        <f t="shared" si="23"/>
+        <v>1482</v>
+      </c>
+      <c r="B1483" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1483" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1483" s="9" t="s">
+        <v>2873</v>
+      </c>
+      <c r="E1483" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1484" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1484">
+        <f t="shared" si="23"/>
+        <v>1483</v>
+      </c>
+      <c r="B1484" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1484" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1484" s="9" t="s">
+        <v>2874</v>
+      </c>
+      <c r="E1484" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1485" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1485">
+        <f t="shared" si="23"/>
+        <v>1484</v>
+      </c>
+      <c r="B1485" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1485" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1485" s="9" t="s">
+        <v>2875</v>
+      </c>
+      <c r="E1485" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1486" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1486">
+        <f t="shared" si="23"/>
+        <v>1485</v>
+      </c>
+      <c r="B1486" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1486" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1486" s="9" t="s">
+        <v>2876</v>
+      </c>
+      <c r="E1486" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1487" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1487">
+        <f t="shared" si="23"/>
+        <v>1486</v>
+      </c>
+      <c r="B1487" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1487" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1487" s="9" t="s">
+        <v>2877</v>
+      </c>
+      <c r="E1487" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1488" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1488">
+        <f t="shared" si="23"/>
+        <v>1487</v>
+      </c>
+      <c r="B1488" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1488" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1488" s="9" t="s">
+        <v>2878</v>
+      </c>
+      <c r="E1488" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1489" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1489">
+        <f t="shared" si="23"/>
+        <v>1488</v>
+      </c>
+      <c r="B1489" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1489" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1489" s="9" t="s">
+        <v>2879</v>
+      </c>
+      <c r="E1489" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1490" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1490">
+        <f t="shared" si="23"/>
+        <v>1489</v>
+      </c>
+      <c r="B1490" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1490" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1490" s="9" t="s">
+        <v>2880</v>
+      </c>
+      <c r="E1490" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1491" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1491">
+        <f t="shared" si="23"/>
+        <v>1490</v>
+      </c>
+      <c r="B1491" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1491" t="s">
+        <v>2849</v>
+      </c>
+      <c r="D1491" s="9" t="s">
+        <v>2881</v>
+      </c>
+      <c r="E1491" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1492" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1492">
+        <f t="shared" si="23"/>
+        <v>1491</v>
+      </c>
+      <c r="B1492" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1492" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1492" s="10" t="s">
+        <v>2883</v>
+      </c>
+      <c r="E1492" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1493" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1493">
+        <f t="shared" si="23"/>
+        <v>1492</v>
+      </c>
+      <c r="B1493" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1493" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1493" s="10" t="s">
+        <v>2884</v>
+      </c>
+      <c r="E1493" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1494" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1494">
+        <f t="shared" si="23"/>
+        <v>1493</v>
+      </c>
+      <c r="B1494" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1494" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1494" s="10" t="s">
+        <v>2885</v>
+      </c>
+      <c r="E1494" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1495" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1495">
+        <f t="shared" si="23"/>
+        <v>1494</v>
+      </c>
+      <c r="B1495" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1495" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1495" s="10" t="s">
+        <v>2886</v>
+      </c>
+      <c r="E1495" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1496" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1496">
+        <f t="shared" si="23"/>
+        <v>1495</v>
+      </c>
+      <c r="B1496" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1496" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1496" s="10" t="s">
+        <v>2887</v>
+      </c>
+      <c r="E1496" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1497" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1497">
+        <f t="shared" si="23"/>
+        <v>1496</v>
+      </c>
+      <c r="B1497" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1497" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1497" s="11" t="s">
+        <v>2888</v>
+      </c>
+      <c r="E1497" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1498">
+        <f t="shared" si="23"/>
+        <v>1497</v>
+      </c>
+      <c r="B1498" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1498" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1498" s="11" t="s">
+        <v>2889</v>
+      </c>
+      <c r="E1498" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1499">
+        <f t="shared" si="23"/>
+        <v>1498</v>
+      </c>
+      <c r="B1499" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1499" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1499" s="11" t="s">
+        <v>2890</v>
+      </c>
+      <c r="E1499" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1500">
+        <f t="shared" si="23"/>
+        <v>1499</v>
+      </c>
+      <c r="B1500" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1500" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1500" s="11" t="s">
+        <v>2891</v>
+      </c>
+      <c r="E1500" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1501">
+        <f t="shared" si="23"/>
+        <v>1500</v>
+      </c>
+      <c r="B1501" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1501" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1501" s="11" t="s">
+        <v>2892</v>
+      </c>
+      <c r="E1501" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1502">
+        <f t="shared" si="23"/>
+        <v>1501</v>
+      </c>
+      <c r="B1502" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1502" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1502" s="11" t="s">
+        <v>2893</v>
+      </c>
+      <c r="E1502" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1503" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1503">
+        <f t="shared" si="23"/>
+        <v>1502</v>
+      </c>
+      <c r="B1503" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1503" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1503" s="11" t="s">
+        <v>2894</v>
+      </c>
+      <c r="E1503" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1504" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1504">
+        <f t="shared" si="23"/>
+        <v>1503</v>
+      </c>
+      <c r="B1504" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1504" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1504" s="11" t="s">
+        <v>2895</v>
+      </c>
+      <c r="E1504" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1505" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1505">
+        <f t="shared" si="23"/>
+        <v>1504</v>
+      </c>
+      <c r="B1505" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1505" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1505" s="11" t="s">
+        <v>2896</v>
+      </c>
+      <c r="E1505" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1506" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1506">
+        <f t="shared" si="23"/>
+        <v>1505</v>
+      </c>
+      <c r="B1506" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1506" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1506" s="11" t="s">
+        <v>2897</v>
+      </c>
+      <c r="E1506" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1507" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1507">
+        <f t="shared" si="23"/>
+        <v>1506</v>
+      </c>
+      <c r="B1507" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1507" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1507" s="11" t="s">
+        <v>2898</v>
+      </c>
+      <c r="E1507" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1508" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1508">
+        <f t="shared" si="23"/>
+        <v>1507</v>
+      </c>
+      <c r="B1508" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1508" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1508" s="11" t="s">
+        <v>2899</v>
+      </c>
+      <c r="E1508" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1509" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1509">
+        <f t="shared" si="23"/>
+        <v>1508</v>
+      </c>
+      <c r="B1509" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1509" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1509" s="11" t="s">
+        <v>2900</v>
+      </c>
+      <c r="E1509" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1510" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1510">
+        <f t="shared" si="23"/>
+        <v>1509</v>
+      </c>
+      <c r="B1510" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1510" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1510" s="11" t="s">
+        <v>2901</v>
+      </c>
+      <c r="E1510" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1511" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1511">
+        <f t="shared" si="23"/>
+        <v>1510</v>
+      </c>
+      <c r="B1511" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1511" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1511" s="11" t="s">
+        <v>2902</v>
+      </c>
+      <c r="E1511" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1512" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1512">
+        <f t="shared" si="23"/>
+        <v>1511</v>
+      </c>
+      <c r="B1512" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1512" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1512" s="11" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1512" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1513" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1513">
+        <f t="shared" si="23"/>
+        <v>1512</v>
+      </c>
+      <c r="B1513" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1513" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1513" s="11" t="s">
+        <v>2903</v>
+      </c>
+      <c r="E1513" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1514" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1514">
+        <f t="shared" si="23"/>
+        <v>1513</v>
+      </c>
+      <c r="B1514" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1514" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1514" s="11" t="s">
+        <v>2904</v>
+      </c>
+      <c r="E1514" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1515" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1515">
+        <f t="shared" si="23"/>
+        <v>1514</v>
+      </c>
+      <c r="B1515" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1515" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1515" s="11" t="s">
+        <v>2905</v>
+      </c>
+      <c r="E1515" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1516" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1516">
+        <f t="shared" si="23"/>
+        <v>1515</v>
+      </c>
+      <c r="B1516" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1516" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1516" s="11" t="s">
+        <v>2906</v>
+      </c>
+      <c r="E1516" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1517" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1517">
+        <f t="shared" si="23"/>
+        <v>1516</v>
+      </c>
+      <c r="B1517" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1517" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1517" s="11" t="s">
+        <v>2907</v>
+      </c>
+      <c r="E1517" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1518" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1518">
+        <f t="shared" si="23"/>
+        <v>1517</v>
+      </c>
+      <c r="B1518" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1518" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1518" s="11" t="s">
+        <v>2908</v>
+      </c>
+      <c r="E1518" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1519" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1519">
+        <f t="shared" si="23"/>
+        <v>1518</v>
+      </c>
+      <c r="B1519" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1519" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1519" s="11" t="s">
+        <v>2909</v>
+      </c>
+      <c r="E1519" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1520" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1520">
+        <f t="shared" si="23"/>
+        <v>1519</v>
+      </c>
+      <c r="B1520" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1520" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1520" s="11" t="s">
+        <v>2910</v>
+      </c>
+      <c r="E1520" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1521" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1521">
+        <f t="shared" si="23"/>
+        <v>1520</v>
+      </c>
+      <c r="B1521" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1521" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1521" s="11" t="s">
+        <v>2911</v>
+      </c>
+      <c r="E1521" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1522" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1522">
+        <f t="shared" si="23"/>
+        <v>1521</v>
+      </c>
+      <c r="B1522" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1522" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1522" s="11" t="s">
+        <v>2912</v>
+      </c>
+      <c r="E1522" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1523" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1523">
+        <f t="shared" si="23"/>
+        <v>1522</v>
+      </c>
+      <c r="B1523" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1523" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1523" s="11" t="s">
+        <v>2913</v>
+      </c>
+      <c r="E1523" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1524" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1524">
+        <f t="shared" si="23"/>
+        <v>1523</v>
+      </c>
+      <c r="B1524" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1524" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1524" s="11" t="s">
+        <v>2914</v>
+      </c>
+      <c r="E1524" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1525" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1525">
+        <f t="shared" si="23"/>
+        <v>1524</v>
+      </c>
+      <c r="B1525" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1525" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1525" s="11" t="s">
+        <v>2915</v>
+      </c>
+      <c r="E1525" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1526" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1526">
+        <f t="shared" si="23"/>
+        <v>1525</v>
+      </c>
+      <c r="B1526" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1526" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1526" s="11" t="s">
+        <v>2916</v>
+      </c>
+      <c r="E1526" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1527" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1527">
+        <f t="shared" si="23"/>
+        <v>1526</v>
+      </c>
+      <c r="B1527" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1527" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1527" s="11" t="s">
+        <v>2917</v>
+      </c>
+      <c r="E1527" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1528" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1528">
+        <f t="shared" si="23"/>
+        <v>1527</v>
+      </c>
+      <c r="B1528" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1528" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1528" s="11" t="s">
+        <v>2918</v>
+      </c>
+      <c r="E1528" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1529" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1529">
+        <f t="shared" si="23"/>
+        <v>1528</v>
+      </c>
+      <c r="B1529" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1529" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1529" s="11" t="s">
+        <v>2919</v>
+      </c>
+      <c r="E1529" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1530" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1530">
+        <f t="shared" si="23"/>
+        <v>1529</v>
+      </c>
+      <c r="B1530" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1530" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1530" s="11" t="s">
+        <v>2920</v>
+      </c>
+      <c r="E1530" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1531" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1531">
+        <f t="shared" si="23"/>
+        <v>1530</v>
+      </c>
+      <c r="B1531" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1531" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1531" s="11" t="s">
+        <v>2921</v>
+      </c>
+      <c r="E1531" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1532" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1532">
+        <f t="shared" si="23"/>
+        <v>1531</v>
+      </c>
+      <c r="B1532" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1532" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1532" s="11" t="s">
+        <v>2922</v>
+      </c>
+      <c r="E1532" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1533" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1533">
+        <f t="shared" si="23"/>
+        <v>1532</v>
+      </c>
+      <c r="B1533" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1533" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1533" s="11" t="s">
+        <v>2923</v>
+      </c>
+      <c r="E1533" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1534" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1534">
+        <f t="shared" si="23"/>
+        <v>1533</v>
+      </c>
+      <c r="B1534" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1534" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1534" s="11" t="s">
+        <v>2924</v>
+      </c>
+      <c r="E1534" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1535" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1535">
+        <f t="shared" si="23"/>
+        <v>1534</v>
+      </c>
+      <c r="B1535" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1535" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1535" s="11" t="s">
+        <v>2925</v>
+      </c>
+      <c r="E1535" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1536" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1536">
+        <f t="shared" si="23"/>
+        <v>1535</v>
+      </c>
+      <c r="B1536" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1536" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1536" s="11" t="s">
+        <v>2926</v>
+      </c>
+      <c r="E1536" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1537" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1537">
+        <f t="shared" si="23"/>
+        <v>1536</v>
+      </c>
+      <c r="B1537" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1537" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1537" s="11" t="s">
+        <v>2927</v>
+      </c>
+      <c r="E1537" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1538" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1538">
+        <f t="shared" si="23"/>
+        <v>1537</v>
+      </c>
+      <c r="B1538" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1538" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1538" s="11" t="s">
+        <v>2928</v>
+      </c>
+      <c r="E1538" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1539" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1539">
+        <f t="shared" si="23"/>
+        <v>1538</v>
+      </c>
+      <c r="B1539" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1539" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1539" s="11" t="s">
+        <v>2929</v>
+      </c>
+      <c r="E1539" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1540" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1540">
+        <f t="shared" ref="A1540:A1603" si="24">A1539+1</f>
+        <v>1539</v>
+      </c>
+      <c r="B1540" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1540" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1540" s="11" t="s">
+        <v>2930</v>
+      </c>
+      <c r="E1540" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1541" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1541">
+        <f t="shared" si="24"/>
+        <v>1540</v>
+      </c>
+      <c r="B1541" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1541" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1541" s="11" t="s">
+        <v>2931</v>
+      </c>
+      <c r="E1541" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1542" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1542">
+        <f t="shared" si="24"/>
+        <v>1541</v>
+      </c>
+      <c r="B1542" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1542" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1542" s="11" t="s">
+        <v>2932</v>
+      </c>
+      <c r="E1542" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1543" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1543">
+        <f t="shared" si="24"/>
+        <v>1542</v>
+      </c>
+      <c r="B1543" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1543" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1543" s="11" t="s">
+        <v>2933</v>
+      </c>
+      <c r="E1543" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1544" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1544">
+        <f t="shared" si="24"/>
+        <v>1543</v>
+      </c>
+      <c r="B1544" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1544" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1544" s="11" t="s">
+        <v>2934</v>
+      </c>
+      <c r="E1544" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1545" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1545">
+        <f t="shared" si="24"/>
+        <v>1544</v>
+      </c>
+      <c r="B1545" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1545" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1545" s="11" t="s">
+        <v>2935</v>
+      </c>
+      <c r="E1545" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1546" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1546">
+        <f t="shared" si="24"/>
+        <v>1545</v>
+      </c>
+      <c r="B1546" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1546" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1546" s="11" t="s">
+        <v>2936</v>
+      </c>
+      <c r="E1546" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1547" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1547">
+        <f t="shared" si="24"/>
+        <v>1546</v>
+      </c>
+      <c r="B1547" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1547" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1547" s="11" t="s">
+        <v>2937</v>
+      </c>
+      <c r="E1547" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1548" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1548">
+        <f t="shared" si="24"/>
+        <v>1547</v>
+      </c>
+      <c r="B1548" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1548" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1548" s="11" t="s">
+        <v>2938</v>
+      </c>
+      <c r="E1548" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1549" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1549">
+        <f t="shared" si="24"/>
+        <v>1548</v>
+      </c>
+      <c r="B1549" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1549" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1549" s="11" t="s">
+        <v>2939</v>
+      </c>
+      <c r="E1549" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1550" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1550">
+        <f t="shared" si="24"/>
+        <v>1549</v>
+      </c>
+      <c r="B1550" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1550" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1550" s="11" t="s">
+        <v>2940</v>
+      </c>
+      <c r="E1550" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1551" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1551">
+        <f t="shared" si="24"/>
+        <v>1550</v>
+      </c>
+      <c r="B1551" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1551" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1551" s="11" t="s">
+        <v>2941</v>
+      </c>
+      <c r="E1551" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1552" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1552">
+        <f t="shared" si="24"/>
+        <v>1551</v>
+      </c>
+      <c r="B1552" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1552" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1552" s="11" t="s">
+        <v>2942</v>
+      </c>
+      <c r="E1552" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1553" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1553">
+        <f t="shared" si="24"/>
+        <v>1552</v>
+      </c>
+      <c r="B1553" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1553" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1553" s="11" t="s">
+        <v>2943</v>
+      </c>
+      <c r="E1553" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1554" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1554">
+        <f t="shared" si="24"/>
+        <v>1553</v>
+      </c>
+      <c r="B1554" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1554" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1554" s="11" t="s">
+        <v>2944</v>
+      </c>
+      <c r="E1554" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1555" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1555">
+        <f t="shared" si="24"/>
+        <v>1554</v>
+      </c>
+      <c r="B1555" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1555" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1555" s="11" t="s">
+        <v>2945</v>
+      </c>
+      <c r="E1555" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1556" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1556">
+        <f t="shared" si="24"/>
+        <v>1555</v>
+      </c>
+      <c r="B1556" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1556" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1556" s="11" t="s">
+        <v>2946</v>
+      </c>
+      <c r="E1556" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1557" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1557">
+        <f t="shared" si="24"/>
+        <v>1556</v>
+      </c>
+      <c r="B1557" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1557" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1557" s="11" t="s">
+        <v>2947</v>
+      </c>
+      <c r="E1557" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1558" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1558">
+        <f t="shared" si="24"/>
+        <v>1557</v>
+      </c>
+      <c r="B1558" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1558" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1558" s="11" t="s">
+        <v>2948</v>
+      </c>
+      <c r="E1558" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1559" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1559">
+        <f t="shared" si="24"/>
+        <v>1558</v>
+      </c>
+      <c r="B1559" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1559" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1559" s="11" t="s">
+        <v>2949</v>
+      </c>
+      <c r="E1559" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1560" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1560">
+        <f t="shared" si="24"/>
+        <v>1559</v>
+      </c>
+      <c r="B1560" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1560" t="s">
+        <v>2882</v>
+      </c>
+      <c r="D1560" s="11" t="s">
+        <v>2950</v>
+      </c>
+      <c r="E1560" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1561" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1561">
+        <f t="shared" si="24"/>
+        <v>1560</v>
+      </c>
+      <c r="B1561" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1561" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1561" s="11" t="s">
+        <v>2952</v>
+      </c>
+      <c r="E1561" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1562" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1562">
+        <f t="shared" si="24"/>
+        <v>1561</v>
+      </c>
+      <c r="B1562" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1562" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1562" s="11" t="s">
+        <v>2953</v>
+      </c>
+      <c r="E1562" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1563" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1563">
+        <f t="shared" si="24"/>
+        <v>1562</v>
+      </c>
+      <c r="B1563" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1563" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1563" s="11" t="s">
+        <v>2954</v>
+      </c>
+      <c r="E1563" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1564" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1564">
+        <f t="shared" si="24"/>
+        <v>1563</v>
+      </c>
+      <c r="B1564" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1564" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1564" s="11" t="s">
+        <v>2955</v>
+      </c>
+      <c r="E1564" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1565" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1565">
+        <f t="shared" si="24"/>
+        <v>1564</v>
+      </c>
+      <c r="B1565" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1565" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1565" s="11" t="s">
+        <v>2956</v>
+      </c>
+      <c r="E1565" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1566" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1566">
+        <f t="shared" si="24"/>
+        <v>1565</v>
+      </c>
+      <c r="B1566" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1566" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1566" s="11" t="s">
+        <v>2957</v>
+      </c>
+      <c r="E1566" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1567" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1567">
+        <f t="shared" si="24"/>
+        <v>1566</v>
+      </c>
+      <c r="B1567" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1567" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1567" s="11" t="s">
+        <v>2958</v>
+      </c>
+      <c r="E1567" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1568" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1568">
+        <f t="shared" si="24"/>
+        <v>1567</v>
+      </c>
+      <c r="B1568" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1568" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1568" s="11" t="s">
+        <v>2959</v>
+      </c>
+      <c r="E1568" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1569" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1569">
+        <f t="shared" si="24"/>
+        <v>1568</v>
+      </c>
+      <c r="B1569" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1569" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1569" s="11" t="s">
+        <v>2960</v>
+      </c>
+      <c r="E1569" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1570" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1570">
+        <f t="shared" si="24"/>
+        <v>1569</v>
+      </c>
+      <c r="B1570" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1570" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1570" s="11" t="s">
+        <v>2961</v>
+      </c>
+      <c r="E1570" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1571" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1571">
+        <f t="shared" si="24"/>
+        <v>1570</v>
+      </c>
+      <c r="B1571" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1571" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1571" s="11" t="s">
+        <v>2962</v>
+      </c>
+      <c r="E1571" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1572" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1572">
+        <f t="shared" si="24"/>
+        <v>1571</v>
+      </c>
+      <c r="B1572" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1572" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1572" s="11" t="s">
+        <v>2963</v>
+      </c>
+      <c r="E1572" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1573" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1573">
+        <f t="shared" si="24"/>
+        <v>1572</v>
+      </c>
+      <c r="B1573" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1573" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1573" s="11" t="s">
+        <v>2964</v>
+      </c>
+      <c r="E1573" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1574" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1574">
+        <f t="shared" si="24"/>
+        <v>1573</v>
+      </c>
+      <c r="B1574" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1574" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1574" s="11" t="s">
+        <v>2965</v>
+      </c>
+      <c r="E1574" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1575" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1575">
+        <f t="shared" si="24"/>
+        <v>1574</v>
+      </c>
+      <c r="B1575" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1575" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1575" s="11" t="s">
+        <v>2966</v>
+      </c>
+      <c r="E1575" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1576" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1576">
+        <f t="shared" si="24"/>
+        <v>1575</v>
+      </c>
+      <c r="B1576" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1576" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1576" s="11" t="s">
+        <v>2967</v>
+      </c>
+      <c r="E1576" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1577" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1577">
+        <f t="shared" si="24"/>
+        <v>1576</v>
+      </c>
+      <c r="B1577" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1577" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1577" s="11" t="s">
+        <v>2968</v>
+      </c>
+      <c r="E1577" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1578" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1578">
+        <f t="shared" si="24"/>
+        <v>1577</v>
+      </c>
+      <c r="B1578" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1578" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1578" s="11" t="s">
+        <v>2969</v>
+      </c>
+      <c r="E1578" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1579" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1579">
+        <f t="shared" si="24"/>
+        <v>1578</v>
+      </c>
+      <c r="B1579" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1579" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1579" s="11" t="s">
+        <v>2970</v>
+      </c>
+      <c r="E1579" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1580" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1580">
+        <f t="shared" si="24"/>
+        <v>1579</v>
+      </c>
+      <c r="B1580" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1580" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1580" s="11" t="s">
+        <v>2971</v>
+      </c>
+      <c r="E1580" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1581" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1581">
+        <f t="shared" si="24"/>
+        <v>1580</v>
+      </c>
+      <c r="B1581" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1581" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1581" s="11" t="s">
+        <v>2972</v>
+      </c>
+      <c r="E1581" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1582" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1582">
+        <f t="shared" si="24"/>
+        <v>1581</v>
+      </c>
+      <c r="B1582" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1582" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1582" s="11" t="s">
+        <v>2973</v>
+      </c>
+      <c r="E1582" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1583" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1583">
+        <f t="shared" si="24"/>
+        <v>1582</v>
+      </c>
+      <c r="B1583" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1583" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1583" s="11" t="s">
+        <v>2974</v>
+      </c>
+      <c r="E1583" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1584" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1584">
+        <f t="shared" si="24"/>
+        <v>1583</v>
+      </c>
+      <c r="B1584" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1584" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1584" s="11" t="s">
+        <v>2975</v>
+      </c>
+      <c r="E1584" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1585" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1585">
+        <f t="shared" si="24"/>
+        <v>1584</v>
+      </c>
+      <c r="B1585" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1585" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1585" s="11" t="s">
+        <v>2976</v>
+      </c>
+      <c r="E1585" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1586" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1586">
+        <f t="shared" si="24"/>
+        <v>1585</v>
+      </c>
+      <c r="B1586" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1586" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1586" s="11" t="s">
+        <v>2977</v>
+      </c>
+      <c r="E1586" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1587" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1587">
+        <f t="shared" si="24"/>
+        <v>1586</v>
+      </c>
+      <c r="B1587" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1587" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1587" s="11" t="s">
+        <v>2978</v>
+      </c>
+      <c r="E1587" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1588" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1588">
+        <f t="shared" si="24"/>
+        <v>1587</v>
+      </c>
+      <c r="B1588" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1588" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1588" s="11" t="s">
+        <v>2979</v>
+      </c>
+      <c r="E1588" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1589" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1589">
+        <f t="shared" si="24"/>
+        <v>1588</v>
+      </c>
+      <c r="B1589" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1589" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1589" s="11" t="s">
+        <v>2980</v>
+      </c>
+      <c r="E1589" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1590" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1590">
+        <f t="shared" si="24"/>
+        <v>1589</v>
+      </c>
+      <c r="B1590" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1590" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1590" s="11" t="s">
+        <v>2981</v>
+      </c>
+      <c r="E1590" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1591" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1591">
+        <f t="shared" si="24"/>
+        <v>1590</v>
+      </c>
+      <c r="B1591" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1591" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1591" s="11" t="s">
+        <v>2982</v>
+      </c>
+      <c r="E1591" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1592" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1592">
+        <f t="shared" si="24"/>
+        <v>1591</v>
+      </c>
+      <c r="B1592" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1592" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1592" s="11" t="s">
+        <v>2983</v>
+      </c>
+      <c r="E1592" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1593" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1593">
+        <f t="shared" si="24"/>
+        <v>1592</v>
+      </c>
+      <c r="B1593" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1593" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1593" s="11" t="s">
+        <v>2984</v>
+      </c>
+      <c r="E1593" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1594" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1594">
+        <f t="shared" si="24"/>
+        <v>1593</v>
+      </c>
+      <c r="B1594" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1594" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1594" s="11" t="s">
+        <v>2985</v>
+      </c>
+      <c r="E1594" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1595" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1595">
+        <f t="shared" si="24"/>
+        <v>1594</v>
+      </c>
+      <c r="B1595" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1595" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1595" s="11" t="s">
+        <v>2986</v>
+      </c>
+      <c r="E1595" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1596" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1596">
+        <f t="shared" si="24"/>
+        <v>1595</v>
+      </c>
+      <c r="B1596" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1596" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1596" s="11" t="s">
+        <v>2987</v>
+      </c>
+      <c r="E1596" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1597" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1597">
+        <f t="shared" si="24"/>
+        <v>1596</v>
+      </c>
+      <c r="B1597" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1597" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1597" s="11" t="s">
+        <v>2988</v>
+      </c>
+      <c r="E1597" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1598" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1598">
+        <f t="shared" si="24"/>
+        <v>1597</v>
+      </c>
+      <c r="B1598" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1598" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1598" s="11" t="s">
+        <v>2989</v>
+      </c>
+      <c r="E1598" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1599" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1599">
+        <f t="shared" si="24"/>
+        <v>1598</v>
+      </c>
+      <c r="B1599" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1599" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1599" s="11" t="s">
+        <v>2990</v>
+      </c>
+      <c r="E1599" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1600" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1600">
+        <f t="shared" si="24"/>
+        <v>1599</v>
+      </c>
+      <c r="B1600" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1600" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1600" s="11" t="s">
+        <v>2991</v>
+      </c>
+      <c r="E1600" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1601" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1601">
+        <f t="shared" si="24"/>
+        <v>1600</v>
+      </c>
+      <c r="B1601" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1601" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1601" s="11" t="s">
+        <v>2992</v>
+      </c>
+      <c r="E1601" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1602" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1602">
+        <f t="shared" si="24"/>
+        <v>1601</v>
+      </c>
+      <c r="B1602" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1602" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1602" s="11" t="s">
+        <v>2993</v>
+      </c>
+      <c r="E1602" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1603" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1603">
+        <f t="shared" si="24"/>
+        <v>1602</v>
+      </c>
+      <c r="B1603" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1603" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1603" s="11" t="s">
+        <v>2994</v>
+      </c>
+      <c r="E1603" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1604" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1604">
+        <f t="shared" ref="A1604:A1667" si="25">A1603+1</f>
+        <v>1603</v>
+      </c>
+      <c r="B1604" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1604" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1604" s="11" t="s">
+        <v>2995</v>
+      </c>
+      <c r="E1604" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1605" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1605">
+        <f t="shared" si="25"/>
+        <v>1604</v>
+      </c>
+      <c r="B1605" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1605" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1605" s="11" t="s">
+        <v>2996</v>
+      </c>
+      <c r="E1605" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1606" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1606">
+        <f t="shared" si="25"/>
+        <v>1605</v>
+      </c>
+      <c r="B1606" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1606" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1606" s="11" t="s">
+        <v>2997</v>
+      </c>
+      <c r="E1606" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1607" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1607">
+        <f t="shared" si="25"/>
+        <v>1606</v>
+      </c>
+      <c r="B1607" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1607" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1607" s="11" t="s">
+        <v>2998</v>
+      </c>
+      <c r="E1607" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1608" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1608">
+        <f t="shared" si="25"/>
+        <v>1607</v>
+      </c>
+      <c r="B1608" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1608" t="s">
+        <v>2951</v>
+      </c>
+      <c r="D1608" s="11" t="s">
+        <v>2999</v>
+      </c>
+      <c r="E1608" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1609" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1609">
+        <f t="shared" si="25"/>
+        <v>1608</v>
+      </c>
+      <c r="B1609" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1609" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1609" s="11" t="s">
+        <v>3001</v>
+      </c>
+      <c r="E1609" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1610" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1610">
+        <f t="shared" si="25"/>
+        <v>1609</v>
+      </c>
+      <c r="B1610" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1610" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1610" s="11" t="s">
+        <v>3002</v>
+      </c>
+      <c r="E1610" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1611" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1611">
+        <f t="shared" si="25"/>
+        <v>1610</v>
+      </c>
+      <c r="B1611" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1611" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1611" s="11" t="s">
+        <v>3003</v>
+      </c>
+      <c r="E1611" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1612" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1612">
+        <f t="shared" si="25"/>
+        <v>1611</v>
+      </c>
+      <c r="B1612" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1612" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1612" s="11" t="s">
+        <v>3004</v>
+      </c>
+      <c r="E1612" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1613" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1613">
+        <f t="shared" si="25"/>
+        <v>1612</v>
+      </c>
+      <c r="B1613" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1613" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1613" s="11" t="s">
+        <v>3005</v>
+      </c>
+      <c r="E1613" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1614" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1614">
+        <f t="shared" si="25"/>
+        <v>1613</v>
+      </c>
+      <c r="B1614" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1614" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1614" s="11" t="s">
+        <v>3006</v>
+      </c>
+      <c r="E1614" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1615" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1615">
+        <f t="shared" si="25"/>
+        <v>1614</v>
+      </c>
+      <c r="B1615" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1615" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1615" s="11" t="s">
+        <v>3007</v>
+      </c>
+      <c r="E1615" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1616" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1616">
+        <f t="shared" si="25"/>
+        <v>1615</v>
+      </c>
+      <c r="B1616" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1616" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1616" s="11" t="s">
+        <v>3008</v>
+      </c>
+      <c r="E1616" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1617" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1617">
+        <f t="shared" si="25"/>
+        <v>1616</v>
+      </c>
+      <c r="B1617" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1617" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1617" s="11" t="s">
+        <v>3009</v>
+      </c>
+      <c r="E1617" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1618" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1618">
+        <f t="shared" si="25"/>
+        <v>1617</v>
+      </c>
+      <c r="B1618" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1618" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1618" s="11" t="s">
+        <v>3010</v>
+      </c>
+      <c r="E1618" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1619" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1619">
+        <f t="shared" si="25"/>
+        <v>1618</v>
+      </c>
+      <c r="B1619" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1619" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1619" s="11" t="s">
+        <v>3011</v>
+      </c>
+      <c r="E1619" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1620" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1620">
+        <f t="shared" si="25"/>
+        <v>1619</v>
+      </c>
+      <c r="B1620" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1620" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1620" s="11" t="s">
+        <v>3012</v>
+      </c>
+      <c r="E1620" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1621" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1621">
+        <f t="shared" si="25"/>
+        <v>1620</v>
+      </c>
+      <c r="B1621" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1621" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1621" s="11" t="s">
+        <v>3013</v>
+      </c>
+      <c r="E1621" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1622" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1622">
+        <f t="shared" si="25"/>
+        <v>1621</v>
+      </c>
+      <c r="B1622" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1622" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1622" s="11" t="s">
+        <v>3014</v>
+      </c>
+      <c r="E1622" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1623" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1623">
+        <f t="shared" si="25"/>
+        <v>1622</v>
+      </c>
+      <c r="B1623" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1623" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1623" s="11" t="s">
+        <v>3015</v>
+      </c>
+      <c r="E1623" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1624" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1624">
+        <f t="shared" si="25"/>
+        <v>1623</v>
+      </c>
+      <c r="B1624" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1624" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1624" s="9" t="s">
+        <v>3016</v>
+      </c>
+      <c r="E1624" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1625" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1625">
+        <f t="shared" si="25"/>
+        <v>1624</v>
+      </c>
+      <c r="B1625" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1625" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1625" s="9" t="s">
+        <v>3017</v>
+      </c>
+      <c r="E1625" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1626" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1626">
+        <f t="shared" si="25"/>
+        <v>1625</v>
+      </c>
+      <c r="B1626" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1626" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1626" s="9" t="s">
+        <v>3018</v>
+      </c>
+      <c r="E1626" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1627" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1627">
+        <f t="shared" si="25"/>
+        <v>1626</v>
+      </c>
+      <c r="B1627" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1627" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1627" s="9" t="s">
+        <v>3019</v>
+      </c>
+      <c r="E1627" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1628" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1628">
+        <f t="shared" si="25"/>
+        <v>1627</v>
+      </c>
+      <c r="B1628" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1628" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1628" s="9" t="s">
+        <v>3020</v>
+      </c>
+      <c r="E1628" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1629" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1629">
+        <f t="shared" si="25"/>
+        <v>1628</v>
+      </c>
+      <c r="B1629" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1629" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1629" s="9" t="s">
+        <v>3021</v>
+      </c>
+      <c r="E1629" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1630" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1630">
+        <f t="shared" si="25"/>
+        <v>1629</v>
+      </c>
+      <c r="B1630" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1630" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1630" s="9" t="s">
+        <v>3022</v>
+      </c>
+      <c r="E1630" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1631" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1631">
+        <f t="shared" si="25"/>
+        <v>1630</v>
+      </c>
+      <c r="B1631" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1631" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1631" s="9" t="s">
+        <v>3023</v>
+      </c>
+      <c r="E1631" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1632" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1632">
+        <f t="shared" si="25"/>
+        <v>1631</v>
+      </c>
+      <c r="B1632" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1632" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1632" s="9" t="s">
+        <v>3024</v>
+      </c>
+      <c r="E1632" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1633" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1633">
+        <f t="shared" si="25"/>
+        <v>1632</v>
+      </c>
+      <c r="B1633" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1633" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1633" s="9" t="s">
+        <v>3025</v>
+      </c>
+      <c r="E1633" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1634" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1634">
+        <f t="shared" si="25"/>
+        <v>1633</v>
+      </c>
+      <c r="B1634" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1634" t="s">
+        <v>3000</v>
+      </c>
+      <c r="D1634" s="9" t="s">
+        <v>3026</v>
+      </c>
+      <c r="E1634" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1635" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1635">
+        <f t="shared" si="25"/>
+        <v>1634</v>
+      </c>
+      <c r="B1635" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1635" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1635" s="12" t="s">
+        <v>3028</v>
+      </c>
+      <c r="E1635" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1636" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1636">
+        <f t="shared" si="25"/>
+        <v>1635</v>
+      </c>
+      <c r="B1636" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1636" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1636" s="12" t="s">
+        <v>3029</v>
+      </c>
+      <c r="E1636" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1637" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1637">
+        <f t="shared" si="25"/>
+        <v>1636</v>
+      </c>
+      <c r="B1637" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1637" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1637" s="12" t="s">
+        <v>3030</v>
+      </c>
+      <c r="E1637" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1638" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1638">
+        <f t="shared" si="25"/>
+        <v>1637</v>
+      </c>
+      <c r="B1638" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1638" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1638" s="12" t="s">
+        <v>3031</v>
+      </c>
+      <c r="E1638" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1639" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1639">
+        <f t="shared" si="25"/>
+        <v>1638</v>
+      </c>
+      <c r="B1639" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1639" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1639" s="12" t="s">
+        <v>3032</v>
+      </c>
+      <c r="E1639" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1640" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1640">
+        <f t="shared" si="25"/>
+        <v>1639</v>
+      </c>
+      <c r="B1640" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1640" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1640" s="12" t="s">
+        <v>3033</v>
+      </c>
+      <c r="E1640" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1641" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1641">
+        <f t="shared" si="25"/>
+        <v>1640</v>
+      </c>
+      <c r="B1641" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1641" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1641" s="12" t="s">
+        <v>3034</v>
+      </c>
+      <c r="E1641" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1642" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1642">
+        <f t="shared" si="25"/>
+        <v>1641</v>
+      </c>
+      <c r="B1642" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1642" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1642" s="12" t="s">
+        <v>3035</v>
+      </c>
+      <c r="E1642" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1643" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1643">
+        <f t="shared" si="25"/>
+        <v>1642</v>
+      </c>
+      <c r="B1643" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1643" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1643" s="12" t="s">
+        <v>3036</v>
+      </c>
+      <c r="E1643" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1644" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1644">
+        <f t="shared" si="25"/>
+        <v>1643</v>
+      </c>
+      <c r="B1644" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1644" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1644" s="12" t="s">
+        <v>3037</v>
+      </c>
+      <c r="E1644" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1645" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1645">
+        <f t="shared" si="25"/>
+        <v>1644</v>
+      </c>
+      <c r="B1645" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1645" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1645" s="12" t="s">
+        <v>3038</v>
+      </c>
+      <c r="E1645" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1646" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1646">
+        <f t="shared" si="25"/>
+        <v>1645</v>
+      </c>
+      <c r="B1646" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1646" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1646" s="12" t="s">
+        <v>3039</v>
+      </c>
+      <c r="E1646" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1647" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1647">
+        <f t="shared" si="25"/>
+        <v>1646</v>
+      </c>
+      <c r="B1647" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1647" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1647" s="12" t="s">
+        <v>3040</v>
+      </c>
+      <c r="E1647" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1648" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1648">
+        <f t="shared" si="25"/>
+        <v>1647</v>
+      </c>
+      <c r="B1648" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1648" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1648" s="12" t="s">
+        <v>3041</v>
+      </c>
+      <c r="E1648" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1649" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1649">
+        <f t="shared" si="25"/>
+        <v>1648</v>
+      </c>
+      <c r="B1649" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1649" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1649" s="12" t="s">
+        <v>3042</v>
+      </c>
+      <c r="E1649" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1650" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1650">
+        <f t="shared" si="25"/>
+        <v>1649</v>
+      </c>
+      <c r="B1650" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1650" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1650" s="12" t="s">
+        <v>3043</v>
+      </c>
+      <c r="E1650" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1651" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1651">
+        <f t="shared" si="25"/>
+        <v>1650</v>
+      </c>
+      <c r="B1651" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1651" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1651" s="12" t="s">
+        <v>3044</v>
+      </c>
+      <c r="E1651" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1652" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1652">
+        <f t="shared" si="25"/>
+        <v>1651</v>
+      </c>
+      <c r="B1652" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1652" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1652" s="12" t="s">
+        <v>3045</v>
+      </c>
+      <c r="E1652" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1653" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1653">
+        <f t="shared" si="25"/>
+        <v>1652</v>
+      </c>
+      <c r="B1653" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1653" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1653" s="12" t="s">
+        <v>3046</v>
+      </c>
+      <c r="E1653" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1654" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1654">
+        <f t="shared" si="25"/>
+        <v>1653</v>
+      </c>
+      <c r="B1654" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1654" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1654" s="12" t="s">
+        <v>3047</v>
+      </c>
+      <c r="E1654" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1655" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1655">
+        <f t="shared" si="25"/>
+        <v>1654</v>
+      </c>
+      <c r="B1655" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1655" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1655" s="12" t="s">
+        <v>3048</v>
+      </c>
+      <c r="E1655" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1656" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1656">
+        <f t="shared" si="25"/>
+        <v>1655</v>
+      </c>
+      <c r="B1656" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1656" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1656" s="12" t="s">
+        <v>3049</v>
+      </c>
+      <c r="E1656" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1657" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1657">
+        <f t="shared" si="25"/>
+        <v>1656</v>
+      </c>
+      <c r="B1657" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1657" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1657" s="12" t="s">
+        <v>3050</v>
+      </c>
+      <c r="E1657" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1658" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1658">
+        <f t="shared" si="25"/>
+        <v>1657</v>
+      </c>
+      <c r="B1658" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1658" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1658" s="12" t="s">
+        <v>3051</v>
+      </c>
+      <c r="E1658" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1659" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1659">
+        <f t="shared" si="25"/>
+        <v>1658</v>
+      </c>
+      <c r="B1659" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1659" t="s">
+        <v>3027</v>
+      </c>
+      <c r="D1659" s="12" t="s">
+        <v>3052</v>
+      </c>
+      <c r="E1659" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1660" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1660">
+        <f t="shared" si="25"/>
+        <v>1659</v>
+      </c>
+      <c r="B1660" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1660" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1660" s="9" t="s">
+        <v>3054</v>
+      </c>
+      <c r="E1660" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1661" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1661">
+        <f t="shared" si="25"/>
+        <v>1660</v>
+      </c>
+      <c r="B1661" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1661" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1661" s="9" t="s">
+        <v>3055</v>
+      </c>
+      <c r="E1661" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1662" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1662">
+        <f t="shared" si="25"/>
+        <v>1661</v>
+      </c>
+      <c r="B1662" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1662" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1662" s="9" t="s">
+        <v>3056</v>
+      </c>
+      <c r="E1662" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1663" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1663">
+        <f t="shared" si="25"/>
+        <v>1662</v>
+      </c>
+      <c r="B1663" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1663" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1663" s="9" t="s">
+        <v>3057</v>
+      </c>
+      <c r="E1663" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1664" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1664">
+        <f t="shared" si="25"/>
+        <v>1663</v>
+      </c>
+      <c r="B1664" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1664" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1664" s="9" t="s">
+        <v>3058</v>
+      </c>
+      <c r="E1664" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1665" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1665">
+        <f t="shared" si="25"/>
+        <v>1664</v>
+      </c>
+      <c r="B1665" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1665" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1665" s="9" t="s">
+        <v>3059</v>
+      </c>
+      <c r="E1665" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1666" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1666">
+        <f t="shared" si="25"/>
+        <v>1665</v>
+      </c>
+      <c r="B1666" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1666" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1666" s="9" t="s">
+        <v>3060</v>
+      </c>
+      <c r="E1666" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1667" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1667">
+        <f t="shared" si="25"/>
+        <v>1666</v>
+      </c>
+      <c r="B1667" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1667" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1667" s="9" t="s">
+        <v>3061</v>
+      </c>
+      <c r="E1667" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1668" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1668">
+        <f t="shared" ref="A1668:A1731" si="26">A1667+1</f>
+        <v>1667</v>
+      </c>
+      <c r="B1668" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1668" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1668" s="9" t="s">
+        <v>3062</v>
+      </c>
+      <c r="E1668" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1669" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1669">
+        <f t="shared" si="26"/>
+        <v>1668</v>
+      </c>
+      <c r="B1669" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1669" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1669" s="9" t="s">
+        <v>3063</v>
+      </c>
+      <c r="E1669" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1670" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1670">
+        <f t="shared" si="26"/>
+        <v>1669</v>
+      </c>
+      <c r="B1670" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1670" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1670" s="9" t="s">
+        <v>3064</v>
+      </c>
+      <c r="E1670" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1671" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1671">
+        <f t="shared" si="26"/>
+        <v>1670</v>
+      </c>
+      <c r="B1671" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1671" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1671" s="9" t="s">
+        <v>3065</v>
+      </c>
+      <c r="E1671" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1672" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1672">
+        <f t="shared" si="26"/>
+        <v>1671</v>
+      </c>
+      <c r="B1672" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1672" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1672" s="9" t="s">
+        <v>3066</v>
+      </c>
+      <c r="E1672" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1673" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1673">
+        <f t="shared" si="26"/>
+        <v>1672</v>
+      </c>
+      <c r="B1673" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1673" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1673" s="9" t="s">
+        <v>3067</v>
+      </c>
+      <c r="E1673" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1674" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1674">
+        <f t="shared" si="26"/>
+        <v>1673</v>
+      </c>
+      <c r="B1674" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1674" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1674" s="9" t="s">
+        <v>3068</v>
+      </c>
+      <c r="E1674" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1675" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1675">
+        <f t="shared" si="26"/>
+        <v>1674</v>
+      </c>
+      <c r="B1675" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1675" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1675" s="9" t="s">
+        <v>3069</v>
+      </c>
+      <c r="E1675" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1676" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1676">
+        <f t="shared" si="26"/>
+        <v>1675</v>
+      </c>
+      <c r="B1676" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1676" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1676" s="9" t="s">
+        <v>3070</v>
+      </c>
+      <c r="E1676" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1677" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1677">
+        <f t="shared" si="26"/>
+        <v>1676</v>
+      </c>
+      <c r="B1677" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1677" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1677" s="9" t="s">
+        <v>3071</v>
+      </c>
+      <c r="E1677" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1678" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1678">
+        <f t="shared" si="26"/>
+        <v>1677</v>
+      </c>
+      <c r="B1678" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1678" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1678" s="9" t="s">
+        <v>3072</v>
+      </c>
+      <c r="E1678" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1679" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1679">
+        <f t="shared" si="26"/>
+        <v>1678</v>
+      </c>
+      <c r="B1679" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1679" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1679" s="9" t="s">
+        <v>3073</v>
+      </c>
+      <c r="E1679" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1680" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1680">
+        <f t="shared" si="26"/>
+        <v>1679</v>
+      </c>
+      <c r="B1680" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1680" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1680" s="9" t="s">
+        <v>3074</v>
+      </c>
+      <c r="E1680" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1681" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1681">
+        <f t="shared" si="26"/>
+        <v>1680</v>
+      </c>
+      <c r="B1681" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1681" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1681" s="9" t="s">
+        <v>3075</v>
+      </c>
+      <c r="E1681" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1682" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1682">
+        <f t="shared" si="26"/>
+        <v>1681</v>
+      </c>
+      <c r="B1682" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1682" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1682" s="9" t="s">
+        <v>3076</v>
+      </c>
+      <c r="E1682" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1683" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1683">
+        <f t="shared" si="26"/>
+        <v>1682</v>
+      </c>
+      <c r="B1683" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1683" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1683" s="9" t="s">
+        <v>3077</v>
+      </c>
+      <c r="E1683" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1684" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1684">
+        <f t="shared" si="26"/>
+        <v>1683</v>
+      </c>
+      <c r="B1684" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1684" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1684" s="9" t="s">
+        <v>3078</v>
+      </c>
+      <c r="E1684" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1685" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1685">
+        <f t="shared" si="26"/>
+        <v>1684</v>
+      </c>
+      <c r="B1685" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1685" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1685" s="9" t="s">
+        <v>3079</v>
+      </c>
+      <c r="E1685" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1686" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1686">
+        <f t="shared" si="26"/>
+        <v>1685</v>
+      </c>
+      <c r="B1686" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1686" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1686" s="9" t="s">
+        <v>3080</v>
+      </c>
+      <c r="E1686" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1687" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1687">
+        <f t="shared" si="26"/>
+        <v>1686</v>
+      </c>
+      <c r="B1687" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1687" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1687" s="9" t="s">
+        <v>3081</v>
+      </c>
+      <c r="E1687" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1688" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1688">
+        <f t="shared" si="26"/>
+        <v>1687</v>
+      </c>
+      <c r="B1688" t="s">
+        <v>2848</v>
+      </c>
+      <c r="C1688" t="s">
+        <v>3053</v>
+      </c>
+      <c r="D1688" s="9" t="s">
+        <v>3082</v>
+      </c>
+      <c r="E1688" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1689" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1689">
+        <f t="shared" si="26"/>
+        <v>1688</v>
+      </c>
+      <c r="B1689" t="s">
+        <v>3083</v>
+      </c>
+      <c r="C1689" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D1689" s="8" t="s">
+        <v>3085</v>
+      </c>
+      <c r="E1689" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1690" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1690">
+        <f t="shared" si="26"/>
+        <v>1689</v>
+      </c>
+      <c r="B1690" t="s">
+        <v>3086</v>
+      </c>
+      <c r="C1690" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D1690" s="8" t="s">
+        <v>3087</v>
+      </c>
+      <c r="E1690" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1691" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1691">
+        <f t="shared" si="26"/>
+        <v>1690</v>
+      </c>
+      <c r="B1691" t="s">
+        <v>3088</v>
+      </c>
+      <c r="C1691" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D1691" s="8" t="s">
+        <v>3089</v>
+      </c>
+      <c r="E1691" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1692" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1692">
+        <f t="shared" si="26"/>
+        <v>1691</v>
+      </c>
+      <c r="B1692" t="s">
+        <v>3090</v>
+      </c>
+      <c r="C1692" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D1692" s="8" t="s">
+        <v>3091</v>
+      </c>
+      <c r="E1692" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1693" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1693">
+        <f t="shared" si="26"/>
+        <v>1692</v>
+      </c>
+      <c r="B1693" t="s">
+        <v>3092</v>
+      </c>
+      <c r="C1693" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D1693" s="8" t="s">
+        <v>3093</v>
+      </c>
+      <c r="E1693" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1694" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1694">
+        <f t="shared" si="26"/>
+        <v>1693</v>
+      </c>
+      <c r="B1694" t="s">
+        <v>3094</v>
+      </c>
+      <c r="C1694" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D1694" s="8" t="s">
+        <v>3095</v>
+      </c>
+      <c r="E1694" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1695" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1695">
+        <f t="shared" si="26"/>
+        <v>1694</v>
+      </c>
+      <c r="B1695" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C1695" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D1695" s="8" t="s">
+        <v>3097</v>
+      </c>
+      <c r="E1695" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1696" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1696">
+        <f t="shared" si="26"/>
+        <v>1695</v>
+      </c>
+      <c r="B1696" t="s">
+        <v>3098</v>
+      </c>
+      <c r="C1696" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D1696" s="8" t="s">
+        <v>3099</v>
+      </c>
+      <c r="E1696" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1697" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1697">
+        <f t="shared" si="26"/>
+        <v>1696</v>
+      </c>
+      <c r="B1697" t="s">
+        <v>3100</v>
+      </c>
+      <c r="C1697" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D1697" s="8" t="s">
+        <v>3101</v>
+      </c>
+      <c r="E1697" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1698" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1698">
+        <f t="shared" si="26"/>
+        <v>1697</v>
+      </c>
+      <c r="B1698" t="s">
+        <v>3102</v>
+      </c>
+      <c r="C1698" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D1698" s="8" t="s">
+        <v>3103</v>
+      </c>
+      <c r="E1698" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1699" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1699">
+        <f t="shared" si="26"/>
+        <v>1698</v>
+      </c>
+      <c r="B1699" t="s">
+        <v>3104</v>
+      </c>
+      <c r="C1699" t="s">
+        <v>3084</v>
+      </c>
+      <c r="D1699" s="8" t="s">
+        <v>3105</v>
+      </c>
+      <c r="E1699" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1700" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1700">
+        <f t="shared" si="26"/>
+        <v>1699</v>
+      </c>
+      <c r="B1700" t="s">
+        <v>3106</v>
+      </c>
+      <c r="C1700" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1700" t="s">
+        <v>3108</v>
+      </c>
+      <c r="E1700" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1701" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1701">
+        <f t="shared" si="26"/>
+        <v>1700</v>
+      </c>
+      <c r="B1701" t="s">
+        <v>3109</v>
+      </c>
+      <c r="C1701" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1701" t="s">
+        <v>3110</v>
+      </c>
+      <c r="E1701" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1702" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1702">
+        <f t="shared" si="26"/>
+        <v>1701</v>
+      </c>
+      <c r="B1702" t="s">
+        <v>3111</v>
+      </c>
+      <c r="C1702" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1702" t="s">
+        <v>3112</v>
+      </c>
+      <c r="E1702" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1703" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1703">
+        <f t="shared" si="26"/>
+        <v>1702</v>
+      </c>
+      <c r="B1703" t="s">
+        <v>3113</v>
+      </c>
+      <c r="C1703" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1703" t="s">
+        <v>3114</v>
+      </c>
+      <c r="E1703" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1704" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1704">
+        <f t="shared" si="26"/>
+        <v>1703</v>
+      </c>
+      <c r="B1704" t="s">
+        <v>3115</v>
+      </c>
+      <c r="C1704" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1704" t="s">
+        <v>3116</v>
+      </c>
+      <c r="E1704" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1705" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1705">
+        <f t="shared" si="26"/>
+        <v>1704</v>
+      </c>
+      <c r="B1705" t="s">
+        <v>3117</v>
+      </c>
+      <c r="C1705" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1705" t="s">
+        <v>3118</v>
+      </c>
+      <c r="E1705" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1706" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1706">
+        <f t="shared" si="26"/>
+        <v>1705</v>
+      </c>
+      <c r="B1706" t="s">
+        <v>3119</v>
+      </c>
+      <c r="C1706" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1706" t="s">
+        <v>3120</v>
+      </c>
+      <c r="E1706" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1707" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1707">
+        <f t="shared" si="26"/>
+        <v>1706</v>
+      </c>
+      <c r="B1707" t="s">
+        <v>3121</v>
+      </c>
+      <c r="C1707" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1707" t="s">
+        <v>3122</v>
+      </c>
+      <c r="E1707" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1708" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1708">
+        <f t="shared" si="26"/>
+        <v>1707</v>
+      </c>
+      <c r="B1708" t="s">
+        <v>3123</v>
+      </c>
+      <c r="C1708" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1708" t="s">
+        <v>3124</v>
+      </c>
+      <c r="E1708" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1709" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1709">
+        <f t="shared" si="26"/>
+        <v>1708</v>
+      </c>
+      <c r="B1709" t="s">
+        <v>3125</v>
+      </c>
+      <c r="C1709" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1709" t="s">
+        <v>3126</v>
+      </c>
+      <c r="E1709" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1710" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1710">
+        <f t="shared" si="26"/>
+        <v>1709</v>
+      </c>
+      <c r="B1710" t="s">
+        <v>3127</v>
+      </c>
+      <c r="C1710" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1710" t="s">
+        <v>3128</v>
+      </c>
+      <c r="E1710" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1711" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1711">
+        <f t="shared" si="26"/>
+        <v>1710</v>
+      </c>
+      <c r="B1711" t="s">
+        <v>3129</v>
+      </c>
+      <c r="C1711" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1711" t="s">
+        <v>3130</v>
+      </c>
+      <c r="E1711" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1712" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1712">
+        <f t="shared" si="26"/>
+        <v>1711</v>
+      </c>
+      <c r="B1712" t="s">
+        <v>3131</v>
+      </c>
+      <c r="C1712" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1712" t="s">
+        <v>3132</v>
+      </c>
+      <c r="E1712" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1713" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1713">
+        <f t="shared" si="26"/>
+        <v>1712</v>
+      </c>
+      <c r="B1713" t="s">
+        <v>3133</v>
+      </c>
+      <c r="C1713" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1713" t="s">
+        <v>3134</v>
+      </c>
+      <c r="E1713" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1714" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1714">
+        <f t="shared" si="26"/>
+        <v>1713</v>
+      </c>
+      <c r="B1714" t="s">
+        <v>3135</v>
+      </c>
+      <c r="C1714" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1714" t="s">
+        <v>3136</v>
+      </c>
+      <c r="E1714" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1715" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1715">
+        <f t="shared" si="26"/>
+        <v>1714</v>
+      </c>
+      <c r="B1715" t="s">
+        <v>3137</v>
+      </c>
+      <c r="C1715" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1715" t="s">
+        <v>3138</v>
+      </c>
+      <c r="E1715" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1716" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1716">
+        <f t="shared" si="26"/>
+        <v>1715</v>
+      </c>
+      <c r="B1716" t="s">
+        <v>3139</v>
+      </c>
+      <c r="C1716" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1716" t="s">
+        <v>3140</v>
+      </c>
+      <c r="E1716" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1717" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1717">
+        <f t="shared" si="26"/>
+        <v>1716</v>
+      </c>
+      <c r="B1717" t="s">
+        <v>3141</v>
+      </c>
+      <c r="C1717" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1717" t="s">
+        <v>3142</v>
+      </c>
+      <c r="E1717" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1718" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1718">
+        <f t="shared" si="26"/>
+        <v>1717</v>
+      </c>
+      <c r="B1718" t="s">
+        <v>3143</v>
+      </c>
+      <c r="C1718" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1718" t="s">
+        <v>3144</v>
+      </c>
+      <c r="E1718" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1719" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1719">
+        <f t="shared" si="26"/>
+        <v>1718</v>
+      </c>
+      <c r="B1719" t="s">
+        <v>3145</v>
+      </c>
+      <c r="C1719" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1719" t="s">
+        <v>3146</v>
+      </c>
+      <c r="E1719" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1720" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1720">
+        <f t="shared" si="26"/>
+        <v>1719</v>
+      </c>
+      <c r="B1720" t="s">
+        <v>3147</v>
+      </c>
+      <c r="C1720" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1720" t="s">
+        <v>3148</v>
+      </c>
+      <c r="E1720" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1721" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1721">
+        <f t="shared" si="26"/>
+        <v>1720</v>
+      </c>
+      <c r="B1721" t="s">
+        <v>3149</v>
+      </c>
+      <c r="C1721" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1721" t="s">
+        <v>3150</v>
+      </c>
+      <c r="E1721" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1722" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1722">
+        <f t="shared" si="26"/>
+        <v>1721</v>
+      </c>
+      <c r="B1722" t="s">
+        <v>3151</v>
+      </c>
+      <c r="C1722" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1722" t="s">
+        <v>3152</v>
+      </c>
+      <c r="E1722" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1723" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1723">
+        <f t="shared" si="26"/>
+        <v>1722</v>
+      </c>
+      <c r="B1723" t="s">
+        <v>3153</v>
+      </c>
+      <c r="C1723" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1723" t="s">
+        <v>3154</v>
+      </c>
+      <c r="E1723" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1724" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1724">
+        <f t="shared" si="26"/>
+        <v>1723</v>
+      </c>
+      <c r="B1724" t="s">
+        <v>3155</v>
+      </c>
+      <c r="C1724" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1724" t="s">
+        <v>3156</v>
+      </c>
+      <c r="E1724" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1725" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1725">
+        <f t="shared" si="26"/>
+        <v>1724</v>
+      </c>
+      <c r="B1725" t="s">
+        <v>3157</v>
+      </c>
+      <c r="C1725" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1725" t="s">
+        <v>3158</v>
+      </c>
+      <c r="E1725" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1726" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1726">
+        <f t="shared" si="26"/>
+        <v>1725</v>
+      </c>
+      <c r="B1726" t="s">
+        <v>3159</v>
+      </c>
+      <c r="C1726" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1726" t="s">
+        <v>3160</v>
+      </c>
+      <c r="E1726" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1727" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1727">
+        <f t="shared" si="26"/>
+        <v>1726</v>
+      </c>
+      <c r="B1727" t="s">
+        <v>3161</v>
+      </c>
+      <c r="C1727" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1727" t="s">
+        <v>3162</v>
+      </c>
+      <c r="E1727" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1728" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1728">
+        <f t="shared" si="26"/>
+        <v>1727</v>
+      </c>
+      <c r="B1728" t="s">
+        <v>3163</v>
+      </c>
+      <c r="C1728" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1728" t="s">
+        <v>3164</v>
+      </c>
+      <c r="E1728" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1729" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1729">
+        <f t="shared" si="26"/>
+        <v>1728</v>
+      </c>
+      <c r="B1729" t="s">
+        <v>3165</v>
+      </c>
+      <c r="C1729" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1729" t="s">
+        <v>3166</v>
+      </c>
+      <c r="E1729" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1730" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1730">
+        <f t="shared" si="26"/>
+        <v>1729</v>
+      </c>
+      <c r="B1730" t="s">
+        <v>3167</v>
+      </c>
+      <c r="C1730" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1730" t="s">
+        <v>3168</v>
+      </c>
+      <c r="E1730" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1731" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1731">
+        <f t="shared" si="26"/>
+        <v>1730</v>
+      </c>
+      <c r="B1731" t="s">
+        <v>3169</v>
+      </c>
+      <c r="C1731" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1731" t="s">
+        <v>3170</v>
+      </c>
+      <c r="E1731" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1732" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1732">
+        <f t="shared" ref="A1732:A1795" si="27">A1731+1</f>
+        <v>1731</v>
+      </c>
+      <c r="B1732" t="s">
+        <v>3171</v>
+      </c>
+      <c r="C1732" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1732" t="s">
+        <v>3172</v>
+      </c>
+      <c r="E1732" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1733" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1733">
+        <f t="shared" si="27"/>
+        <v>1732</v>
+      </c>
+      <c r="B1733" t="s">
+        <v>3173</v>
+      </c>
+      <c r="C1733" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1733" t="s">
+        <v>3174</v>
+      </c>
+      <c r="E1733" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1734" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1734">
+        <f t="shared" si="27"/>
+        <v>1733</v>
+      </c>
+      <c r="B1734" t="s">
+        <v>3175</v>
+      </c>
+      <c r="C1734" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1734" t="s">
+        <v>3176</v>
+      </c>
+      <c r="E1734" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1735" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1735">
+        <f t="shared" si="27"/>
+        <v>1734</v>
+      </c>
+      <c r="B1735" t="s">
+        <v>3177</v>
+      </c>
+      <c r="C1735" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1735" t="s">
+        <v>3178</v>
+      </c>
+      <c r="E1735" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1736" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1736">
+        <f t="shared" si="27"/>
+        <v>1735</v>
+      </c>
+      <c r="B1736" t="s">
+        <v>3179</v>
+      </c>
+      <c r="C1736" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1736" t="s">
+        <v>3180</v>
+      </c>
+      <c r="E1736" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1737" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1737">
+        <f t="shared" si="27"/>
+        <v>1736</v>
+      </c>
+      <c r="B1737" t="s">
+        <v>3181</v>
+      </c>
+      <c r="C1737" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1737" t="s">
+        <v>3182</v>
+      </c>
+      <c r="E1737" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1738" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1738">
+        <f t="shared" si="27"/>
+        <v>1737</v>
+      </c>
+      <c r="B1738" t="s">
+        <v>3183</v>
+      </c>
+      <c r="C1738" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1738" t="s">
+        <v>3184</v>
+      </c>
+      <c r="E1738" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1739" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1739">
+        <f t="shared" si="27"/>
+        <v>1738</v>
+      </c>
+      <c r="B1739" t="s">
+        <v>3185</v>
+      </c>
+      <c r="C1739" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1739" t="s">
+        <v>3186</v>
+      </c>
+      <c r="E1739" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1740" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1740">
+        <f t="shared" si="27"/>
+        <v>1739</v>
+      </c>
+      <c r="B1740" t="s">
+        <v>3187</v>
+      </c>
+      <c r="C1740" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1740" t="s">
+        <v>3188</v>
+      </c>
+      <c r="E1740" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1741" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1741">
+        <f t="shared" si="27"/>
+        <v>1740</v>
+      </c>
+      <c r="B1741" t="s">
+        <v>3189</v>
+      </c>
+      <c r="C1741" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1741" t="s">
+        <v>3190</v>
+      </c>
+      <c r="E1741" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1742" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1742">
+        <f t="shared" si="27"/>
+        <v>1741</v>
+      </c>
+      <c r="B1742" t="s">
+        <v>3191</v>
+      </c>
+      <c r="C1742" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1742" s="8" t="s">
+        <v>3192</v>
+      </c>
+      <c r="E1742" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1743" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1743">
+        <f t="shared" si="27"/>
+        <v>1742</v>
+      </c>
+      <c r="B1743" t="s">
+        <v>3193</v>
+      </c>
+      <c r="C1743" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1743" s="8" t="s">
+        <v>3194</v>
+      </c>
+      <c r="E1743" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1744" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1744">
+        <f t="shared" si="27"/>
+        <v>1743</v>
+      </c>
+      <c r="B1744" t="s">
+        <v>3195</v>
+      </c>
+      <c r="C1744" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1744" s="8" t="s">
+        <v>3196</v>
+      </c>
+      <c r="E1744" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1745" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1745">
+        <f t="shared" si="27"/>
+        <v>1744</v>
+      </c>
+      <c r="B1745" t="s">
+        <v>3197</v>
+      </c>
+      <c r="C1745" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1745" s="8" t="s">
+        <v>3198</v>
+      </c>
+      <c r="E1745" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1746" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1746">
+        <f t="shared" si="27"/>
+        <v>1745</v>
+      </c>
+      <c r="B1746" t="s">
+        <v>3199</v>
+      </c>
+      <c r="C1746" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1746" s="8" t="s">
+        <v>3200</v>
+      </c>
+      <c r="E1746" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1747" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1747">
+        <f t="shared" si="27"/>
+        <v>1746</v>
+      </c>
+      <c r="B1747" t="s">
+        <v>3201</v>
+      </c>
+      <c r="C1747" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1747" s="8" t="s">
+        <v>3202</v>
+      </c>
+      <c r="E1747" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1748" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1748">
+        <f t="shared" si="27"/>
+        <v>1747</v>
+      </c>
+      <c r="B1748" t="s">
+        <v>3203</v>
+      </c>
+      <c r="C1748" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1748" s="8" t="s">
+        <v>3204</v>
+      </c>
+      <c r="E1748" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1749" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1749">
+        <f t="shared" si="27"/>
+        <v>1748</v>
+      </c>
+      <c r="B1749" t="s">
+        <v>3205</v>
+      </c>
+      <c r="C1749" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1749" s="8" t="s">
+        <v>3206</v>
+      </c>
+      <c r="E1749" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1750" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1750">
+        <f t="shared" si="27"/>
+        <v>1749</v>
+      </c>
+      <c r="B1750" t="s">
+        <v>3207</v>
+      </c>
+      <c r="C1750" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1750" s="8" t="s">
+        <v>3208</v>
+      </c>
+      <c r="E1750" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1751" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1751">
+        <f t="shared" si="27"/>
+        <v>1750</v>
+      </c>
+      <c r="B1751" t="s">
+        <v>3209</v>
+      </c>
+      <c r="C1751" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1751" s="8" t="s">
+        <v>3210</v>
+      </c>
+      <c r="E1751" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1752" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1752">
+        <f t="shared" si="27"/>
+        <v>1751</v>
+      </c>
+      <c r="B1752" t="s">
+        <v>3211</v>
+      </c>
+      <c r="C1752" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1752"/>
+      <c r="E1752" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1753" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1753">
+        <f t="shared" si="27"/>
+        <v>1752</v>
+      </c>
+      <c r="B1753" t="s">
+        <v>3212</v>
+      </c>
+      <c r="C1753" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1753" s="8" t="s">
+        <v>3213</v>
+      </c>
+      <c r="E1753" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1754" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1754">
+        <f t="shared" si="27"/>
+        <v>1753</v>
+      </c>
+      <c r="B1754" t="s">
+        <v>3214</v>
+      </c>
+      <c r="C1754" t="s">
+        <v>3107</v>
+      </c>
+      <c r="D1754" s="8" t="s">
+        <v>3215</v>
+      </c>
+      <c r="E1754" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1755" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1755">
+        <f t="shared" si="27"/>
+        <v>1754</v>
+      </c>
+      <c r="B1755" t="s">
+        <v>3216</v>
+      </c>
+      <c r="C1755" t="s">
+        <v>3217</v>
+      </c>
+      <c r="D1755" s="8" t="s">
+        <v>3218</v>
+      </c>
+      <c r="E1755" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1756" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1756">
+        <f t="shared" si="27"/>
+        <v>1755</v>
+      </c>
+      <c r="B1756" t="s">
+        <v>3219</v>
+      </c>
+      <c r="C1756" t="s">
+        <v>3217</v>
+      </c>
+      <c r="D1756" s="8" t="s">
+        <v>3220</v>
+      </c>
+      <c r="E1756" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1757" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1757">
+        <f t="shared" si="27"/>
+        <v>1756</v>
+      </c>
+      <c r="B1757" t="s">
+        <v>3221</v>
+      </c>
+      <c r="C1757" t="s">
+        <v>3217</v>
+      </c>
+      <c r="D1757" s="8" t="s">
+        <v>3222</v>
+      </c>
+      <c r="E1757" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1758" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1758">
+        <f t="shared" si="27"/>
+        <v>1757</v>
+      </c>
+      <c r="B1758" t="s">
+        <v>3223</v>
+      </c>
+      <c r="C1758" t="s">
+        <v>3217</v>
+      </c>
+      <c r="D1758" s="8" t="s">
+        <v>3224</v>
+      </c>
+      <c r="E1758" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1759" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1759">
+        <f t="shared" si="27"/>
+        <v>1758</v>
+      </c>
+      <c r="B1759" t="s">
+        <v>3225</v>
+      </c>
+      <c r="C1759" t="s">
+        <v>3217</v>
+      </c>
+      <c r="D1759" s="8" t="s">
+        <v>3226</v>
+      </c>
+      <c r="E1759" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1760" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1760">
+        <f t="shared" si="27"/>
+        <v>1759</v>
+      </c>
+      <c r="B1760" t="s">
+        <v>3227</v>
+      </c>
+      <c r="C1760" t="s">
+        <v>3217</v>
+      </c>
+      <c r="D1760" s="8" t="s">
+        <v>3228</v>
+      </c>
+      <c r="E1760" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1761" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1761">
+        <f t="shared" si="27"/>
+        <v>1760</v>
+      </c>
+      <c r="B1761" t="s">
+        <v>3229</v>
+      </c>
+      <c r="C1761" t="s">
+        <v>3217</v>
+      </c>
+      <c r="D1761" s="8" t="s">
+        <v>3230</v>
+      </c>
+      <c r="E1761" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1762" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1762">
+        <f t="shared" si="27"/>
+        <v>1761</v>
+      </c>
+      <c r="B1762" t="s">
+        <v>3231</v>
+      </c>
+      <c r="C1762" t="s">
+        <v>3217</v>
+      </c>
+      <c r="D1762" s="8" t="s">
+        <v>3232</v>
+      </c>
+      <c r="E1762" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1763" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1763">
+        <f t="shared" si="27"/>
+        <v>1762</v>
+      </c>
+      <c r="B1763" t="s">
+        <v>3233</v>
+      </c>
+      <c r="C1763" t="s">
+        <v>3217</v>
+      </c>
+      <c r="D1763" s="8" t="s">
+        <v>3234</v>
+      </c>
+      <c r="E1763" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1764" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1764">
+        <f t="shared" si="27"/>
+        <v>1763</v>
+      </c>
+      <c r="B1764" t="s">
+        <v>3235</v>
+      </c>
+      <c r="C1764" t="s">
+        <v>3217</v>
+      </c>
+      <c r="D1764" s="8" t="s">
+        <v>3236</v>
+      </c>
+      <c r="E1764" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1765" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1765">
+        <f t="shared" si="27"/>
+        <v>1764</v>
+      </c>
+      <c r="B1765" t="s">
+        <v>3237</v>
+      </c>
+      <c r="C1765" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1765" s="8" t="s">
+        <v>3239</v>
+      </c>
+      <c r="E1765" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1766" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1766">
+        <f t="shared" si="27"/>
+        <v>1765</v>
+      </c>
+      <c r="B1766" t="s">
+        <v>3240</v>
+      </c>
+      <c r="C1766" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1766"/>
+      <c r="E1766" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1767" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1767">
+        <f t="shared" si="27"/>
+        <v>1766</v>
+      </c>
+      <c r="B1767" t="s">
+        <v>3241</v>
+      </c>
+      <c r="C1767" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1767" s="8" t="s">
+        <v>3242</v>
+      </c>
+      <c r="E1767" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1768" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1768">
+        <f t="shared" si="27"/>
+        <v>1767</v>
+      </c>
+      <c r="B1768" t="s">
+        <v>3243</v>
+      </c>
+      <c r="C1768" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1768" s="8" t="s">
+        <v>3244</v>
+      </c>
+      <c r="E1768" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1769" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1769">
+        <f t="shared" si="27"/>
+        <v>1768</v>
+      </c>
+      <c r="B1769" t="s">
+        <v>3245</v>
+      </c>
+      <c r="C1769" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1769" s="8" t="s">
+        <v>3246</v>
+      </c>
+      <c r="E1769" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1770" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1770">
+        <f t="shared" si="27"/>
+        <v>1769</v>
+      </c>
+      <c r="B1770" t="s">
+        <v>3247</v>
+      </c>
+      <c r="C1770" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1770" s="8" t="s">
+        <v>3248</v>
+      </c>
+      <c r="E1770" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1771" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1771">
+        <f t="shared" si="27"/>
+        <v>1770</v>
+      </c>
+      <c r="B1771" t="s">
+        <v>3249</v>
+      </c>
+      <c r="C1771" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1771" s="8" t="s">
+        <v>3250</v>
+      </c>
+      <c r="E1771" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1772" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1772">
+        <f t="shared" si="27"/>
+        <v>1771</v>
+      </c>
+      <c r="B1772" t="s">
+        <v>3251</v>
+      </c>
+      <c r="C1772" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1772" s="8" t="s">
+        <v>3252</v>
+      </c>
+      <c r="E1772" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1773" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1773">
+        <f t="shared" si="27"/>
+        <v>1772</v>
+      </c>
+      <c r="B1773" t="s">
+        <v>3253</v>
+      </c>
+      <c r="C1773" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1773" s="8" t="s">
+        <v>3254</v>
+      </c>
+      <c r="E1773" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1774" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1774">
+        <f t="shared" si="27"/>
+        <v>1773</v>
+      </c>
+      <c r="B1774" t="s">
+        <v>3255</v>
+      </c>
+      <c r="C1774" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1774" s="8" t="s">
+        <v>3256</v>
+      </c>
+      <c r="E1774" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1775" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1775">
+        <f t="shared" si="27"/>
+        <v>1774</v>
+      </c>
+      <c r="B1775" t="s">
+        <v>3257</v>
+      </c>
+      <c r="C1775" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1775" s="8" t="s">
+        <v>3258</v>
+      </c>
+      <c r="E1775" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1776" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1776">
+        <f t="shared" si="27"/>
+        <v>1775</v>
+      </c>
+      <c r="B1776" t="s">
+        <v>3259</v>
+      </c>
+      <c r="C1776" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1776" s="8" t="s">
+        <v>3260</v>
+      </c>
+      <c r="E1776" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1777" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1777">
+        <f t="shared" si="27"/>
+        <v>1776</v>
+      </c>
+      <c r="B1777" t="s">
+        <v>3261</v>
+      </c>
+      <c r="C1777" t="s">
+        <v>3238</v>
+      </c>
+      <c r="D1777" s="8" t="s">
+        <v>3262</v>
+      </c>
+      <c r="E1777" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1778" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1778">
+        <f t="shared" si="27"/>
+        <v>1777</v>
+      </c>
+      <c r="B1778" t="s">
+        <v>3263</v>
+      </c>
+      <c r="C1778" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1778" s="8" t="s">
+        <v>3265</v>
+      </c>
+      <c r="E1778" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1779" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1779">
+        <f t="shared" si="27"/>
+        <v>1778</v>
+      </c>
+      <c r="B1779" t="s">
+        <v>3266</v>
+      </c>
+      <c r="C1779" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1779" s="8" t="s">
+        <v>3267</v>
+      </c>
+      <c r="E1779" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1780" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1780">
+        <f t="shared" si="27"/>
+        <v>1779</v>
+      </c>
+      <c r="B1780" t="s">
+        <v>3268</v>
+      </c>
+      <c r="C1780" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1780" s="8" t="s">
+        <v>3269</v>
+      </c>
+      <c r="E1780" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1781" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1781">
+        <f t="shared" si="27"/>
+        <v>1780</v>
+      </c>
+      <c r="B1781" t="s">
+        <v>3270</v>
+      </c>
+      <c r="C1781" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1781" s="8" t="s">
+        <v>3271</v>
+      </c>
+      <c r="E1781" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1782" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1782">
+        <f t="shared" si="27"/>
+        <v>1781</v>
+      </c>
+      <c r="B1782" t="s">
+        <v>3272</v>
+      </c>
+      <c r="C1782" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1782" s="8" t="s">
+        <v>3273</v>
+      </c>
+      <c r="E1782" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1783" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1783">
+        <f t="shared" si="27"/>
+        <v>1782</v>
+      </c>
+      <c r="B1783" t="s">
+        <v>3274</v>
+      </c>
+      <c r="C1783" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1783" s="8" t="s">
+        <v>3275</v>
+      </c>
+      <c r="E1783" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1784" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1784">
+        <f t="shared" si="27"/>
+        <v>1783</v>
+      </c>
+      <c r="B1784" t="s">
+        <v>3276</v>
+      </c>
+      <c r="C1784" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1784" s="8" t="s">
+        <v>3277</v>
+      </c>
+      <c r="E1784" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1785" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1785">
+        <f t="shared" si="27"/>
+        <v>1784</v>
+      </c>
+      <c r="B1785" t="s">
+        <v>3278</v>
+      </c>
+      <c r="C1785" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1785" s="8" t="s">
+        <v>3279</v>
+      </c>
+      <c r="E1785" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1786" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1786">
+        <f t="shared" si="27"/>
+        <v>1785</v>
+      </c>
+      <c r="B1786" t="s">
+        <v>3280</v>
+      </c>
+      <c r="C1786" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1786" s="8" t="s">
+        <v>3281</v>
+      </c>
+      <c r="E1786" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1787" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1787">
+        <f t="shared" si="27"/>
+        <v>1786</v>
+      </c>
+      <c r="B1787" t="s">
+        <v>3282</v>
+      </c>
+      <c r="C1787" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1787" s="8" t="s">
+        <v>3283</v>
+      </c>
+      <c r="E1787" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1788" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1788">
+        <f t="shared" si="27"/>
+        <v>1787</v>
+      </c>
+      <c r="B1788" t="s">
+        <v>3284</v>
+      </c>
+      <c r="C1788" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1788" s="8" t="s">
+        <v>3285</v>
+      </c>
+      <c r="E1788" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1789" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1789">
+        <f t="shared" si="27"/>
+        <v>1788</v>
+      </c>
+      <c r="B1789" t="s">
+        <v>3286</v>
+      </c>
+      <c r="C1789" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1789" s="8" t="s">
+        <v>3287</v>
+      </c>
+      <c r="E1789" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1790" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1790">
+        <f t="shared" si="27"/>
+        <v>1789</v>
+      </c>
+      <c r="B1790" t="s">
+        <v>3288</v>
+      </c>
+      <c r="C1790" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1790" s="8" t="s">
+        <v>3289</v>
+      </c>
+      <c r="E1790" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1791" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1791">
+        <f t="shared" si="27"/>
+        <v>1790</v>
+      </c>
+      <c r="B1791" t="s">
+        <v>3290</v>
+      </c>
+      <c r="C1791" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1791" s="8" t="s">
+        <v>3291</v>
+      </c>
+      <c r="E1791" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1792" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1792">
+        <f t="shared" si="27"/>
+        <v>1791</v>
+      </c>
+      <c r="B1792" t="s">
+        <v>3292</v>
+      </c>
+      <c r="C1792" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1792" s="8" t="s">
+        <v>3293</v>
+      </c>
+      <c r="E1792" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1793" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1793">
+        <f t="shared" si="27"/>
+        <v>1792</v>
+      </c>
+      <c r="B1793" t="s">
+        <v>3294</v>
+      </c>
+      <c r="C1793" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1793" s="8" t="s">
+        <v>3295</v>
+      </c>
+      <c r="E1793" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1794" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1794">
+        <f t="shared" si="27"/>
+        <v>1793</v>
+      </c>
+      <c r="B1794" t="s">
+        <v>3296</v>
+      </c>
+      <c r="C1794" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1794" s="8" t="s">
+        <v>3297</v>
+      </c>
+      <c r="E1794" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1795" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1795">
+        <f t="shared" si="27"/>
+        <v>1794</v>
+      </c>
+      <c r="B1795" t="s">
+        <v>3298</v>
+      </c>
+      <c r="C1795" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1795" s="8" t="s">
+        <v>3299</v>
+      </c>
+      <c r="E1795" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1796" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1796">
+        <f t="shared" ref="A1796:A1809" si="28">A1795+1</f>
+        <v>1795</v>
+      </c>
+      <c r="B1796" t="s">
+        <v>3300</v>
+      </c>
+      <c r="C1796" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1796" s="8" t="s">
+        <v>3301</v>
+      </c>
+      <c r="E1796" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1797" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1797">
+        <f t="shared" si="28"/>
+        <v>1796</v>
+      </c>
+      <c r="B1797" t="s">
+        <v>3302</v>
+      </c>
+      <c r="C1797" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1797" s="8" t="s">
+        <v>3303</v>
+      </c>
+      <c r="E1797" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1798" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1798">
+        <f t="shared" si="28"/>
+        <v>1797</v>
+      </c>
+      <c r="B1798" t="s">
+        <v>3304</v>
+      </c>
+      <c r="C1798" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1798" s="8" t="s">
+        <v>3305</v>
+      </c>
+      <c r="E1798" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1799" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1799">
+        <f t="shared" si="28"/>
+        <v>1798</v>
+      </c>
+      <c r="B1799" t="s">
+        <v>3306</v>
+      </c>
+      <c r="C1799" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1799" s="8" t="s">
+        <v>3307</v>
+      </c>
+      <c r="E1799" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1800" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1800">
+        <f t="shared" si="28"/>
+        <v>1799</v>
+      </c>
+      <c r="B1800" t="s">
+        <v>3308</v>
+      </c>
+      <c r="C1800" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1800" s="8" t="s">
+        <v>3309</v>
+      </c>
+      <c r="E1800" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1801" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1801">
+        <f t="shared" si="28"/>
+        <v>1800</v>
+      </c>
+      <c r="B1801" t="s">
+        <v>3310</v>
+      </c>
+      <c r="C1801" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1801" s="8" t="s">
+        <v>3311</v>
+      </c>
+      <c r="E1801" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1802" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1802">
+        <f t="shared" si="28"/>
+        <v>1801</v>
+      </c>
+      <c r="B1802" t="s">
+        <v>3312</v>
+      </c>
+      <c r="C1802" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1802" s="8" t="s">
+        <v>3313</v>
+      </c>
+      <c r="E1802" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1803" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1803">
+        <f t="shared" si="28"/>
+        <v>1802</v>
+      </c>
+      <c r="B1803" t="s">
+        <v>3314</v>
+      </c>
+      <c r="C1803" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1803" s="8" t="s">
+        <v>3315</v>
+      </c>
+      <c r="E1803" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1804" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1804">
+        <f t="shared" si="28"/>
+        <v>1803</v>
+      </c>
+      <c r="B1804" t="s">
+        <v>3316</v>
+      </c>
+      <c r="C1804" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1804" s="8" t="s">
+        <v>3317</v>
+      </c>
+      <c r="E1804" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1805" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1805">
+        <f t="shared" si="28"/>
+        <v>1804</v>
+      </c>
+      <c r="B1805" t="s">
+        <v>3318</v>
+      </c>
+      <c r="C1805" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1805" s="8" t="s">
+        <v>3319</v>
+      </c>
+      <c r="E1805" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1806" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1806">
+        <f t="shared" si="28"/>
+        <v>1805</v>
+      </c>
+      <c r="B1806" t="s">
+        <v>3320</v>
+      </c>
+      <c r="C1806" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1806" s="8" t="s">
+        <v>3321</v>
+      </c>
+      <c r="E1806" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1807" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1807">
+        <f t="shared" si="28"/>
+        <v>1806</v>
+      </c>
+      <c r="B1807" t="s">
+        <v>3322</v>
+      </c>
+      <c r="C1807" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1807" s="8" t="s">
+        <v>3323</v>
+      </c>
+      <c r="E1807" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1808" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1808">
+        <f t="shared" si="28"/>
+        <v>1807</v>
+      </c>
+      <c r="B1808" t="s">
+        <v>3324</v>
+      </c>
+      <c r="C1808" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1808" s="8" t="s">
+        <v>3325</v>
+      </c>
+      <c r="E1808" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1809" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A1809">
+        <f t="shared" si="28"/>
+        <v>1808</v>
+      </c>
+      <c r="B1809" t="s">
+        <v>3326</v>
+      </c>
+      <c r="C1809" t="s">
+        <v>3264</v>
+      </c>
+      <c r="D1809" s="8" t="s">
+        <v>3327</v>
+      </c>
+      <c r="E1809" t="s">
         <v>25</v>
       </c>
     </row>
@@ -35249,7 +42998,7 @@
     </filterColumn>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
-  <conditionalFormatting sqref="B2:B10 D2:E2 B11:C505 D3:D34 G4:M14 G16:M20 G15:H15 J15:M15 H2:M3 E3:E1459">
+  <conditionalFormatting sqref="B2:B10 D2:E2 B11:C505 D3:D34 G4:M14 G16:M20 G15:H15 J15:M15 H2:M3 E3:E1809">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -35279,7 +43028,7 @@
               <x14:axisColor rgb="FF000000"/>
             </x14:dataBar>
           </x14:cfRule>
-          <xm:sqref>B2:B10 D2:E2 B11:C505 D3:D34 G4:M14 G16:M20 G15:H15 J15:M15 H2:M3 E3:E1459</xm:sqref>
+          <xm:sqref>B2:B10 D2:E2 B11:C505 D3:D34 G4:M14 G16:M20 G15:H15 J15:M15 H2:M3 E3:E1809</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
